--- a/salida/justificacion/Justificacion de medidas planos.xlsx
+++ b/salida/justificacion/Justificacion de medidas planos.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Manuales ABC'!$2:$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rodantes ABC'!$A$3:$L$96</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Rodantes ABC'!$2:$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Revendidos'!$A$3:$V$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Revendidos'!$A$3:$V$114</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Revendidos'!$2:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Fuentes'!$3:$3</definedName>
   </definedNames>
@@ -391,7 +391,7 @@
     </comment>
     <comment ref="F4" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 415; diferencia -13 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 415; diferencia -14 %)</t>
       </text>
     </comment>
     <comment ref="H4" authorId="0" shapeId="0">
@@ -406,22 +406,22 @@
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 92; diferencia +45 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 92; diferencia +41 %)</t>
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 220; diferencia -8 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 220; diferencia -9 %)</t>
       </text>
     </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -4 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -5 %)</t>
       </text>
     </comment>
     <comment ref="J5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia +0 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia -1 %)</t>
       </text>
     </comment>
     <comment ref="D6" authorId="0" shapeId="0">
@@ -584,24 +584,44 @@
         <t>Rosca del racor medida en Fadesa</t>
       </text>
     </comment>
-    <comment ref="D51" authorId="0" shapeId="0">
-      <text>
-        <t>Medido a escala; cara superior a 27 mm del cuerpo</t>
-      </text>
-    </comment>
-    <comment ref="F51" authorId="0" shapeId="0">
-      <text>
-        <t>Medido a escala; cara superior a 41.5 mm del cuerpo</t>
-      </text>
-    </comment>
-    <comment ref="H51" authorId="0" shapeId="0">
-      <text>
-        <t>Medido a escala; cara superior a 41.5 mm del cuerpo</t>
-      </text>
-    </comment>
-    <comment ref="J51" authorId="0" shapeId="0">
-      <text>
-        <t>Medido a escala; cara superior a 41.5 mm del cuerpo</t>
+    <comment ref="D53" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (31 puntos), no una caja</t>
+      </text>
+    </comment>
+    <comment ref="F53" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (47 puntos), no una caja</t>
+      </text>
+    </comment>
+    <comment ref="H53" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (47 puntos), no una caja</t>
+      </text>
+    </comment>
+    <comment ref="J53" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (47 puntos), no una caja</t>
+      </text>
+    </comment>
+    <comment ref="D55" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (40 puntos), no una caja</t>
+      </text>
+    </comment>
+    <comment ref="F55" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (37 puntos), no una caja</t>
+      </text>
+    </comment>
+    <comment ref="H55" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (37 puntos), no una caja</t>
+      </text>
+    </comment>
+    <comment ref="J55" authorId="0" shapeId="0">
+      <text>
+        <t>Contorno completo extraído del plano vectorial Fadesa (37 puntos), no una caja</t>
       </text>
     </comment>
     <comment ref="D65" authorId="0" shapeId="0">
@@ -1154,42 +1174,42 @@
         <t>Interno: no se ve en el plano Fadesa (G763)</t>
       </text>
     </comment>
-    <comment ref="D78" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="F78" authorId="0" shapeId="0">
+    <comment ref="D74" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="F74" authorId="0" shapeId="0">
       <text>
         <t>Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
       </text>
     </comment>
-    <comment ref="H78" authorId="0" shapeId="0">
+    <comment ref="H74" authorId="0" shapeId="0">
       <text>
         <t>Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
       </text>
     </comment>
-    <comment ref="J78" authorId="0" shapeId="0">
+    <comment ref="J74" authorId="0" shapeId="0">
       <text>
         <t>Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
       </text>
     </comment>
-    <comment ref="D79" authorId="0" shapeId="0">
+    <comment ref="D75" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="F79" authorId="0" shapeId="0">
+    <comment ref="F75" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
       </text>
     </comment>
-    <comment ref="H79" authorId="0" shapeId="0">
+    <comment ref="H75" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
       </text>
     </comment>
-    <comment ref="J79" authorId="0" shapeId="0">
+    <comment ref="J75" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
       </text>
@@ -1291,12 +1311,12 @@
     </comment>
     <comment ref="D5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia -4 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia -5 %)</t>
       </text>
     </comment>
     <comment ref="F5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia +1 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia -1 %)</t>
       </text>
     </comment>
     <comment ref="H5" authorId="0" shapeId="0">
@@ -1306,17 +1326,17 @@
     </comment>
     <comment ref="J5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -4 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -5 %)</t>
       </text>
     </comment>
     <comment ref="L5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 270; diferencia -14 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 270; diferencia -15 %)</t>
       </text>
     </comment>
     <comment ref="N5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 254; diferencia -5 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 254; diferencia -6 %)</t>
       </text>
     </comment>
     <comment ref="P5" authorId="0" shapeId="0">
@@ -1326,12 +1346,12 @@
     </comment>
     <comment ref="R5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -4 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -5 %)</t>
       </text>
     </comment>
     <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia +7 %)</t>
+        <t>Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia +5 %)</t>
       </text>
     </comment>
     <comment ref="D6" authorId="0" shapeId="0">
@@ -2169,92 +2189,92 @@
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="D82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="F82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="H82" authorId="0" shapeId="0">
+    <comment ref="D78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="F78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="H78" authorId="0" shapeId="0">
       <text>
         <t>Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
       </text>
     </comment>
-    <comment ref="J82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="L82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="N82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="P82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="R82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="T82" authorId="0" shapeId="0">
-      <text>
-        <t>Pasa por la horquilla; sin cota en Fadesa</t>
-      </text>
-    </comment>
-    <comment ref="D83" authorId="0" shapeId="0">
+    <comment ref="J78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="L78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="N78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="P78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="R78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="T78" authorId="0" shapeId="0">
+      <text>
+        <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
+      </text>
+    </comment>
+    <comment ref="D79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="F83" authorId="0" shapeId="0">
+    <comment ref="F79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="H83" authorId="0" shapeId="0">
+    <comment ref="H79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
       </text>
     </comment>
-    <comment ref="J83" authorId="0" shapeId="0">
+    <comment ref="J79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="L83" authorId="0" shapeId="0">
+    <comment ref="L79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="N83" authorId="0" shapeId="0">
+    <comment ref="N79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="P83" authorId="0" shapeId="0">
+    <comment ref="P79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="R83" authorId="0" shapeId="0">
+    <comment ref="R79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
     </comment>
-    <comment ref="T83" authorId="0" shapeId="0">
+    <comment ref="T79" authorId="0" shapeId="0">
       <text>
         <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
       </text>
@@ -2349,132 +2369,132 @@
         <t>Desde la espiga hasta 18 mm sobre el fondo</t>
       </text>
     </comment>
-    <comment ref="D93" authorId="0" shapeId="0">
+    <comment ref="D94" authorId="0" shapeId="0">
       <text>
         <t>Sin cota en Fadesa</t>
       </text>
     </comment>
-    <comment ref="F93" authorId="0" shapeId="0">
+    <comment ref="F94" authorId="0" shapeId="0">
       <text>
         <t>Sin cota en Fadesa</t>
       </text>
     </comment>
-    <comment ref="H93" authorId="0" shapeId="0">
+    <comment ref="H94" authorId="0" shapeId="0">
       <text>
         <t>Sin cota en Fadesa</t>
       </text>
     </comment>
-    <comment ref="J93" authorId="0" shapeId="0">
+    <comment ref="J94" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="L93" authorId="0" shapeId="0">
+    <comment ref="L94" authorId="0" shapeId="0">
       <text>
         <t>Sin cota en Fadesa</t>
       </text>
     </comment>
-    <comment ref="P93" authorId="0" shapeId="0">
+    <comment ref="P94" authorId="0" shapeId="0">
       <text>
         <t>Sin cota en Fadesa</t>
       </text>
     </comment>
-    <comment ref="R93" authorId="0" shapeId="0">
+    <comment ref="R94" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="T93" authorId="0" shapeId="0">
+    <comment ref="T94" authorId="0" shapeId="0">
       <text>
         <t>Sin cota en Fadesa</t>
       </text>
     </comment>
-    <comment ref="D104" authorId="0" shapeId="0">
+    <comment ref="D105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(95)</t>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0">
+    <comment ref="F105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(95)</t>
       </text>
     </comment>
-    <comment ref="H104" authorId="0" shapeId="0">
+    <comment ref="H105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(160)</t>
       </text>
     </comment>
-    <comment ref="J104" authorId="0" shapeId="0">
+    <comment ref="J105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(76.5)</t>
       </text>
     </comment>
-    <comment ref="L104" authorId="0" shapeId="0">
+    <comment ref="L105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(95)</t>
       </text>
     </comment>
-    <comment ref="N104" authorId="0" shapeId="0">
+    <comment ref="N105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(57)</t>
       </text>
     </comment>
-    <comment ref="P104" authorId="0" shapeId="0">
+    <comment ref="P105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(70)</t>
       </text>
     </comment>
-    <comment ref="R104" authorId="0" shapeId="0">
+    <comment ref="R105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(76.5)</t>
       </text>
     </comment>
-    <comment ref="T104" authorId="0" shapeId="0">
+    <comment ref="T105" authorId="0" shapeId="0">
       <text>
         <t>108° × π/180 × R(90.75)</t>
       </text>
     </comment>
-    <comment ref="D111" authorId="0" shapeId="0">
+    <comment ref="D112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="F111" authorId="0" shapeId="0">
+    <comment ref="F112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="H111" authorId="0" shapeId="0">
+    <comment ref="H112" authorId="0" shapeId="0">
       <text>
         <t>Interno: no se ve en el plano Fadesa (G763)</t>
       </text>
     </comment>
-    <comment ref="J111" authorId="0" shapeId="0">
+    <comment ref="J112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="L111" authorId="0" shapeId="0">
+    <comment ref="L112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="N111" authorId="0" shapeId="0">
+    <comment ref="N112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="P111" authorId="0" shapeId="0">
+    <comment ref="P112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="R111" authorId="0" shapeId="0">
+    <comment ref="R112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
     </comment>
-    <comment ref="T111" authorId="0" shapeId="0">
+    <comment ref="T112" authorId="0" shapeId="0">
       <text>
         <t>Medido a escala en el plano Fadesa</t>
       </text>
@@ -2853,7 +2873,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Total: 1134 dimensiones — con documento 753 (66 %), diseño FLAMA 293 (26 %), a validar 88 (8 %).</t>
+          <t>Total: 1137 dimensiones — con documento 753 (66 %), diseño FLAMA 296 (26 %), a validar 88 (8 %).</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3165,7 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>328</v>
+        <v>327.4</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -3153,7 +3173,7 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>359.1</v>
+        <v>358.7</v>
       </c>
       <c r="G4" s="16" t="inlineStr">
         <is>
@@ -3161,7 +3181,7 @@
         </is>
       </c>
       <c r="H4" s="15" t="n">
-        <v>435.1</v>
+        <v>434.7</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -3169,7 +3189,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>608.1</v>
+        <v>607.7</v>
       </c>
       <c r="K4" s="16" t="inlineStr">
         <is>
@@ -3195,7 +3215,7 @@
         </is>
       </c>
       <c r="D5" s="21" t="n">
-        <v>133.5</v>
+        <v>130</v>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
@@ -3203,7 +3223,7 @@
         </is>
       </c>
       <c r="F5" s="21" t="n">
-        <v>202.2</v>
+        <v>199.2</v>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
@@ -3211,7 +3231,7 @@
         </is>
       </c>
       <c r="H5" s="21" t="n">
-        <v>216.7</v>
+        <v>213.7</v>
       </c>
       <c r="I5" s="22" t="inlineStr">
         <is>
@@ -3219,7 +3239,7 @@
         </is>
       </c>
       <c r="J5" s="21" t="n">
-        <v>230.9</v>
+        <v>228</v>
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
@@ -3228,7 +3248,7 @@
       </c>
       <c r="L5" s="23" t="inlineStr">
         <is>
-          <t>ABC 1 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 92; diferencia +45 %) · ABC 2.5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 220; diferencia -8 %) · ABC 5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -4 %) · ABC 10 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia +0 %)</t>
+          <t>ABC 1 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 92; diferencia +41 %) · ABC 2.5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 220; diferencia -9 %) · ABC 5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -5 %) · ABC 10 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia -1 %)</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3365,7 @@
         </is>
       </c>
       <c r="D8" s="21" t="n">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
@@ -3353,7 +3373,7 @@
         </is>
       </c>
       <c r="F8" s="21" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -3361,7 +3381,7 @@
         </is>
       </c>
       <c r="H8" s="21" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="I8" s="24" t="inlineStr">
         <is>
@@ -3369,7 +3389,7 @@
         </is>
       </c>
       <c r="J8" s="21" t="n">
-        <v>6.23</v>
+        <v>6.14</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -5150,7 +5170,7 @@
       </c>
       <c r="D43" s="28" t="inlineStr">
         <is>
-          <t>31 × 12</t>
+          <t>26 × 15</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
@@ -5160,7 +5180,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
@@ -5170,7 +5190,7 @@
       </c>
       <c r="H43" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="I43" s="16" t="inlineStr">
@@ -5180,7 +5200,7 @@
       </c>
       <c r="J43" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr">
@@ -5219,7 +5239,7 @@
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="H44" s="31" t="n">
@@ -5227,7 +5247,7 @@
       </c>
       <c r="I44" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="J44" s="31" t="n">
@@ -5235,7 +5255,7 @@
       </c>
       <c r="K44" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="L44" s="23" t="inlineStr">
@@ -5248,7 +5268,7 @@
       <c r="A45" s="18" t="inlineStr"/>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>Horquilla del pivote (alto)</t>
+          <t>Oreja del pivote: ancho / eje a (x, z)</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -5256,32 +5276,40 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D45" s="21" t="n">
-        <v>26.5</v>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>18 / (-10,4; 21,43)</t>
+        </is>
       </c>
       <c r="E45" s="22" t="inlineStr">
         <is>
           <t>F07·3</t>
         </is>
       </c>
-      <c r="F45" s="21" t="n">
-        <v>32.2</v>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="G45" s="22" t="inlineStr">
         <is>
           <t>F08·3</t>
         </is>
       </c>
-      <c r="H45" s="21" t="n">
-        <v>32.2</v>
+      <c r="H45" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="I45" s="22" t="inlineStr">
         <is>
           <t>F09·3</t>
         </is>
       </c>
-      <c r="J45" s="21" t="n">
-        <v>32.2</v>
+      <c r="J45" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="K45" s="22" t="inlineStr">
         <is>
@@ -5290,7 +5318,7 @@
       </c>
       <c r="L45" s="23" t="inlineStr">
         <is>
-          <t>Medido a escala</t>
+          <t>Centro del agujero del pivote medido en el plano Fadesa; ancho de diseño</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5336,7 @@
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>12 × 9</t>
+          <t>10,8 × 7,3</t>
         </is>
       </c>
       <c r="E46" s="30" t="inlineStr">
@@ -5591,12 +5619,12 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Manija de accionamiento</t>
+          <t>Eje de palanca</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>Largo × alto (palanca)</t>
+          <t>Ø × largo</t>
         </is>
       </c>
       <c r="C51" s="14" t="inlineStr">
@@ -5604,111 +5632,123 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>67 × 6</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="inlineStr">
-        <is>
-          <t>F07·3</t>
-        </is>
-      </c>
-      <c r="F51" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="inlineStr">
-        <is>
-          <t>F08·3</t>
-        </is>
-      </c>
-      <c r="H51" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="J51" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="K51" s="16" t="inlineStr">
-        <is>
-          <t>F10·3</t>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>3,6 × 29</t>
+        </is>
+      </c>
+      <c r="E51" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="F51" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="G51" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="H51" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="I51" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="J51" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="K51" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
         </is>
       </c>
       <c r="L51" s="17" t="inlineStr">
         <is>
-          <t>ABC 1 kg: Medido a escala; cara superior a 27 mm del cuerpo (cada modelo con sus valores: ver el comentario)</t>
+          <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr"/>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>Ancho de la chapa</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Pasador de seguridad</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>Ø alambre × largo</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D52" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="E52" s="30" t="inlineStr">
-        <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="F52" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="G52" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="H52" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="I52" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="J52" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="K52" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="L52" s="23" t="inlineStr">
-        <is>
-          <t>No visible en la vista lateral</t>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 40,5</t>
+        </is>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="F52" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="G52" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="H52" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="I52" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="J52" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="K52" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="L52" s="17" t="inlineStr">
+        <is>
+          <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Manija de transporte</t>
+          <t>Manija de accionamiento</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>Tramos de la manija fija</t>
+          <t>Perfil lateral: largo × alto (x / z extremos)</t>
         </is>
       </c>
       <c r="C53" s="14" t="inlineStr">
@@ -5718,7 +5758,7 @@
       </c>
       <c r="D53" s="28" t="inlineStr">
         <is>
-          <t>49 + 27</t>
+          <t>67,1 × 11,0 (-15,8 a 51,3 / 16,0 a 27,0)</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -5728,7 +5768,7 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
@@ -5738,7 +5778,7 @@
       </c>
       <c r="H53" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="I53" s="16" t="inlineStr">
@@ -5748,7 +5788,7 @@
       </c>
       <c r="J53" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="K53" s="16" t="inlineStr">
@@ -5758,7 +5798,7 @@
       </c>
       <c r="L53" s="17" t="inlineStr">
         <is>
-          <t>Medido a escala en el plano Fadesa</t>
+          <t>ABC 1 kg: Contorno completo extraído del plano vectorial Fadesa (31 puntos), no una caja (cada modelo con sus valores: ver el comentario)</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5806,7 @@
       <c r="A54" s="18" t="inlineStr"/>
       <c r="B54" s="19" t="inlineStr">
         <is>
-          <t>Ancho de la chapa</t>
+          <t>Ancho (chapa estampada en U)</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
@@ -5774,53 +5814,61 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D54" s="31" t="n">
-        <v>14</v>
+      <c r="D54" s="29" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>D02</t>
-        </is>
-      </c>
-      <c r="F54" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="F54" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="G54" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="H54" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="H54" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="I54" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="J54" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="J54" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K54" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="L54" s="23" t="inlineStr">
         <is>
-          <t>No visible en la vista lateral</t>
+          <t>No visible en la vista lateral: a horcajadas del cuerpo (palanca) y de la palanca (manija)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>Eje de palanca</t>
+          <t>Manija de transporte</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>Ø × largo</t>
+          <t>Perfil lateral: largo × alto (x / z extremos)</t>
         </is>
       </c>
       <c r="C55" s="14" t="inlineStr">
@@ -5828,111 +5876,107 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
-        <is>
-          <t>1,8 × 30</t>
-        </is>
-      </c>
-      <c r="E55" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="F55" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="G55" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="H55" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="I55" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="J55" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="K55" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
+      <c r="D55" s="28" t="inlineStr">
+        <is>
+          <t>91,6 × 60,0 (-0,2 a 91,5 / -30,7 a 29,3)</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="inlineStr">
+        <is>
+          <t>F07·3</t>
+        </is>
+      </c>
+      <c r="F55" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>F08·3</t>
+        </is>
+      </c>
+      <c r="H55" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="J55" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>F10·3</t>
         </is>
       </c>
       <c r="L55" s="17" t="inlineStr">
         <is>
-          <t>Pasa por la horquilla; sin cota en Fadesa</t>
+          <t>ABC 1 kg: Contorno completo extraído del plano vectorial Fadesa (40 puntos), no una caja (cada modelo con sus valores: ver el comentario)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>Pasador de seguridad</t>
-        </is>
-      </c>
-      <c r="B56" s="13" t="inlineStr">
-        <is>
-          <t>Ø alambre × largo</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
+      <c r="A56" s="18" t="inlineStr"/>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>Ancho (chapa estampada en U)</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D56" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 40</t>
-        </is>
-      </c>
-      <c r="E56" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="F56" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="G56" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="H56" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="I56" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="J56" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="K56" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="L56" s="17" t="inlineStr">
-        <is>
-          <t>Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2)</t>
+      <c r="D56" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="F56" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G56" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="H56" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="J56" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K56" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="L56" s="23" t="inlineStr">
+        <is>
+          <t>No visible en la vista lateral: a horcajadas del cuerpo (palanca) y de la palanca (manija)</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6213,7 @@
       </c>
       <c r="E61" s="27" t="n"/>
       <c r="F61" s="21" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
@@ -6177,7 +6221,7 @@
         </is>
       </c>
       <c r="H61" s="21" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I61" s="24" t="inlineStr">
         <is>
@@ -6185,7 +6229,7 @@
         </is>
       </c>
       <c r="J61" s="21" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K61" s="24" t="inlineStr">
         <is>
@@ -6337,7 +6381,7 @@
       </c>
       <c r="E64" s="33" t="inlineStr">
         <is>
-          <t>D06</t>
+          <t>D07</t>
         </is>
       </c>
       <c r="F64" s="34" t="inlineStr">
@@ -6909,7 +6953,7 @@
       </c>
       <c r="E74" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="F74" s="32" t="inlineStr">
@@ -6919,7 +6963,7 @@
       </c>
       <c r="G74" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="H74" s="32" t="inlineStr">
@@ -6929,7 +6973,7 @@
       </c>
       <c r="I74" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="J74" s="32" t="inlineStr">
@@ -6939,7 +6983,7 @@
       </c>
       <c r="K74" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="L74" s="17" t="inlineStr">
@@ -7544,7 +7588,7 @@
         </is>
       </c>
       <c r="D8" s="21" t="n">
-        <v>31.22</v>
+        <v>31.15</v>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
@@ -7552,7 +7596,7 @@
         </is>
       </c>
       <c r="F8" s="21" t="n">
-        <v>42.63</v>
+        <v>42.57</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -7560,7 +7604,7 @@
         </is>
       </c>
       <c r="H8" s="21" t="n">
-        <v>67.92</v>
+        <v>67.86</v>
       </c>
       <c r="I8" s="24" t="inlineStr">
         <is>
@@ -7568,7 +7612,7 @@
         </is>
       </c>
       <c r="J8" s="21" t="n">
-        <v>89.44</v>
+        <v>89.38</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -8518,7 +8562,7 @@
       </c>
       <c r="E27" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="F27" s="31" t="n">
@@ -8526,7 +8570,7 @@
       </c>
       <c r="G27" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="H27" s="31" t="n">
@@ -8534,7 +8578,7 @@
       </c>
       <c r="I27" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="J27" s="31" t="n">
@@ -8542,7 +8586,7 @@
       </c>
       <c r="K27" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="L27" s="23" t="inlineStr">
@@ -8772,7 +8816,7 @@
       </c>
       <c r="E32" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="F32" s="31" t="n">
@@ -8780,7 +8824,7 @@
       </c>
       <c r="G32" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="H32" s="31" t="n">
@@ -8788,7 +8832,7 @@
       </c>
       <c r="I32" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="J32" s="31" t="n">
@@ -8796,7 +8840,7 @@
       </c>
       <c r="K32" s="30" t="inlineStr">
         <is>
-          <t>D36</t>
+          <t>D38</t>
         </is>
       </c>
       <c r="L32" s="23" t="inlineStr">
@@ -9190,7 +9234,7 @@
       </c>
       <c r="E40" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D15</t>
+          <t>F38·6 + D17</t>
         </is>
       </c>
       <c r="F40" s="32" t="inlineStr">
@@ -9200,7 +9244,7 @@
       </c>
       <c r="G40" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D15</t>
+          <t>F38·6 + D17</t>
         </is>
       </c>
       <c r="H40" s="32" t="inlineStr">
@@ -9210,7 +9254,7 @@
       </c>
       <c r="I40" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D15</t>
+          <t>F38·6 + D17</t>
         </is>
       </c>
       <c r="J40" s="32" t="inlineStr">
@@ -9220,7 +9264,7 @@
       </c>
       <c r="K40" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D15</t>
+          <t>F38·6 + D17</t>
         </is>
       </c>
       <c r="L40" s="17" t="inlineStr">
@@ -9400,7 +9444,7 @@
       </c>
       <c r="K44" s="30" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="L44" s="23" t="inlineStr">
@@ -9574,7 +9618,7 @@
       </c>
       <c r="E48" s="30" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="F48" s="31" t="n">
@@ -9582,7 +9626,7 @@
       </c>
       <c r="G48" s="30" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="H48" s="31" t="n">
@@ -9590,7 +9634,7 @@
       </c>
       <c r="I48" s="30" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="J48" s="26" t="inlineStr">
@@ -9626,7 +9670,7 @@
       </c>
       <c r="E49" s="33" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="F49" s="41" t="n">
@@ -9634,7 +9678,7 @@
       </c>
       <c r="G49" s="33" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="H49" s="41" t="n">
@@ -9642,7 +9686,7 @@
       </c>
       <c r="I49" s="33" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="J49" s="41" t="n">
@@ -9650,7 +9694,7 @@
       </c>
       <c r="K49" s="33" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="L49" s="17" t="inlineStr">
@@ -9678,7 +9722,7 @@
       </c>
       <c r="E50" s="30" t="inlineStr">
         <is>
-          <t>D18 + F11·1</t>
+          <t>D20 + F11·1</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
@@ -9688,7 +9732,7 @@
       </c>
       <c r="G50" s="30" t="inlineStr">
         <is>
-          <t>D18 + F11·1</t>
+          <t>D20 + F11·1</t>
         </is>
       </c>
       <c r="H50" s="29" t="inlineStr">
@@ -9698,7 +9742,7 @@
       </c>
       <c r="I50" s="30" t="inlineStr">
         <is>
-          <t>D18 + F11·1</t>
+          <t>D20 + F11·1</t>
         </is>
       </c>
       <c r="J50" s="29" t="inlineStr">
@@ -9708,7 +9752,7 @@
       </c>
       <c r="K50" s="30" t="inlineStr">
         <is>
-          <t>D18 + F11·1</t>
+          <t>D20 + F11·1</t>
         </is>
       </c>
       <c r="L50" s="23" t="inlineStr">
@@ -9736,7 +9780,7 @@
       </c>
       <c r="E51" s="30" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
@@ -9746,7 +9790,7 @@
       </c>
       <c r="G51" s="30" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="H51" s="29" t="inlineStr">
@@ -9756,7 +9800,7 @@
       </c>
       <c r="I51" s="30" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="J51" s="29" t="inlineStr">
@@ -9766,7 +9810,7 @@
       </c>
       <c r="K51" s="30" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="L51" s="23" t="inlineStr">
@@ -9798,7 +9842,7 @@
       </c>
       <c r="E52" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + F40·1 + D20</t>
+          <t>F38·6 + F40·1 + D22</t>
         </is>
       </c>
       <c r="F52" s="32" t="inlineStr">
@@ -9808,7 +9852,7 @@
       </c>
       <c r="G52" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + F40·1 + D20</t>
+          <t>F38·6 + F40·1 + D22</t>
         </is>
       </c>
       <c r="H52" s="32" t="inlineStr">
@@ -9818,7 +9862,7 @@
       </c>
       <c r="I52" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + F40·1 + D20</t>
+          <t>F38·6 + F40·1 + D22</t>
         </is>
       </c>
       <c r="J52" s="32" t="inlineStr">
@@ -9828,7 +9872,7 @@
       </c>
       <c r="K52" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + F40·1 + D20</t>
+          <t>F38·6 + F40·1 + D22</t>
         </is>
       </c>
       <c r="L52" s="17" t="inlineStr">
@@ -9860,7 +9904,7 @@
       </c>
       <c r="E53" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D21</t>
+          <t>F38·6 + D23</t>
         </is>
       </c>
       <c r="F53" s="32" t="inlineStr">
@@ -9870,7 +9914,7 @@
       </c>
       <c r="G53" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D21</t>
+          <t>F38·6 + D23</t>
         </is>
       </c>
       <c r="H53" s="32" t="inlineStr">
@@ -9880,7 +9924,7 @@
       </c>
       <c r="I53" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D21</t>
+          <t>F38·6 + D23</t>
         </is>
       </c>
       <c r="J53" s="32" t="inlineStr">
@@ -9890,7 +9934,7 @@
       </c>
       <c r="K53" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D21</t>
+          <t>F38·6 + D23</t>
         </is>
       </c>
       <c r="L53" s="17" t="inlineStr">
@@ -9922,7 +9966,7 @@
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D22</t>
+          <t>F38·6 + D24</t>
         </is>
       </c>
       <c r="F54" s="32" t="inlineStr">
@@ -9932,7 +9976,7 @@
       </c>
       <c r="G54" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D22</t>
+          <t>F38·6 + D24</t>
         </is>
       </c>
       <c r="H54" s="32" t="inlineStr">
@@ -9942,7 +9986,7 @@
       </c>
       <c r="I54" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D22</t>
+          <t>F38·6 + D24</t>
         </is>
       </c>
       <c r="J54" s="32" t="inlineStr">
@@ -9952,7 +9996,7 @@
       </c>
       <c r="K54" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D22</t>
+          <t>F38·6 + D24</t>
         </is>
       </c>
       <c r="L54" s="17" t="inlineStr">
@@ -9978,7 +10022,7 @@
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D23</t>
+          <t>F38·6 + D25</t>
         </is>
       </c>
       <c r="F55" s="31" t="n">
@@ -9986,7 +10030,7 @@
       </c>
       <c r="G55" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D23</t>
+          <t>F38·6 + D25</t>
         </is>
       </c>
       <c r="H55" s="31" t="n">
@@ -9994,7 +10038,7 @@
       </c>
       <c r="I55" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D23</t>
+          <t>F38·6 + D25</t>
         </is>
       </c>
       <c r="J55" s="31" t="n">
@@ -10002,7 +10046,7 @@
       </c>
       <c r="K55" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D23</t>
+          <t>F38·6 + D25</t>
         </is>
       </c>
       <c r="L55" s="23" t="inlineStr">
@@ -10034,7 +10078,7 @@
       </c>
       <c r="E56" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="F56" s="32" t="inlineStr">
@@ -10044,7 +10088,7 @@
       </c>
       <c r="G56" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="H56" s="32" t="inlineStr">
@@ -10054,7 +10098,7 @@
       </c>
       <c r="I56" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="J56" s="32" t="inlineStr">
@@ -10064,7 +10108,7 @@
       </c>
       <c r="K56" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="L56" s="17" t="inlineStr">
@@ -10142,7 +10186,7 @@
       </c>
       <c r="E58" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
@@ -10152,7 +10196,7 @@
       </c>
       <c r="G58" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="H58" s="29" t="inlineStr">
@@ -10162,7 +10206,7 @@
       </c>
       <c r="I58" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="J58" s="29" t="inlineStr">
@@ -10172,7 +10216,7 @@
       </c>
       <c r="K58" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="L58" s="23" t="inlineStr">
@@ -10204,7 +10248,7 @@
       </c>
       <c r="E59" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D25</t>
+          <t>F38·6 + D27</t>
         </is>
       </c>
       <c r="F59" s="32" t="inlineStr">
@@ -10214,7 +10258,7 @@
       </c>
       <c r="G59" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D25</t>
+          <t>F38·6 + D27</t>
         </is>
       </c>
       <c r="H59" s="32" t="inlineStr">
@@ -10224,7 +10268,7 @@
       </c>
       <c r="I59" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D25</t>
+          <t>F38·6 + D27</t>
         </is>
       </c>
       <c r="J59" s="32" t="inlineStr">
@@ -10234,7 +10278,7 @@
       </c>
       <c r="K59" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D25</t>
+          <t>F38·6 + D27</t>
         </is>
       </c>
       <c r="L59" s="17" t="inlineStr">
@@ -10264,7 +10308,7 @@
       </c>
       <c r="E60" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="F60" s="41" t="n">
@@ -10272,7 +10316,7 @@
       </c>
       <c r="G60" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="H60" s="41" t="n">
@@ -10280,7 +10324,7 @@
       </c>
       <c r="I60" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="J60" s="41" t="n">
@@ -10288,7 +10332,7 @@
       </c>
       <c r="K60" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="L60" s="17" t="inlineStr">
@@ -10489,7 +10533,7 @@
       </c>
       <c r="D64" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
@@ -10550,7 +10594,7 @@
       </c>
       <c r="E65" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="F65" s="31" t="n">
@@ -10558,7 +10602,7 @@
       </c>
       <c r="G65" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="H65" s="31" t="n">
@@ -10566,7 +10610,7 @@
       </c>
       <c r="I65" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J65" s="31" t="n">
@@ -10574,7 +10618,7 @@
       </c>
       <c r="K65" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="L65" s="23" t="inlineStr">
@@ -10587,7 +10631,7 @@
       <c r="A66" s="18" t="inlineStr"/>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>Horquilla del pivote (alto)</t>
+          <t>Oreja del pivote: ancho / eje a (x, z)</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -10595,8 +10639,10 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D66" s="21" t="n">
-        <v>32.2</v>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="E66" s="22" t="inlineStr">
         <is>
@@ -10623,7 +10669,7 @@
       <c r="K66" s="27" t="n"/>
       <c r="L66" s="23" t="inlineStr">
         <is>
-          <t>Medido a escala</t>
+          <t>Centro del agujero del pivote medido en el plano Fadesa; ancho de diseño</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10702,7 @@
       </c>
       <c r="G67" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="H67" s="29" t="inlineStr">
@@ -10666,7 +10712,7 @@
       </c>
       <c r="I67" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J67" s="29" t="inlineStr">
@@ -10676,7 +10722,7 @@
       </c>
       <c r="K67" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="L67" s="23" t="inlineStr">
@@ -10884,7 +10930,7 @@
       </c>
       <c r="G71" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="H71" s="32" t="inlineStr">
@@ -10894,7 +10940,7 @@
       </c>
       <c r="I71" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J71" s="32" t="inlineStr">
@@ -10904,7 +10950,7 @@
       </c>
       <c r="K71" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="L71" s="17" t="inlineStr">
@@ -10946,7 +10992,7 @@
       </c>
       <c r="G72" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="H72" s="32" t="inlineStr">
@@ -10956,7 +11002,7 @@
       </c>
       <c r="I72" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J72" s="32" t="inlineStr">
@@ -10966,7 +11012,7 @@
       </c>
       <c r="K72" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="L72" s="17" t="inlineStr">
@@ -11004,7 +11050,7 @@
       </c>
       <c r="G73" s="33" t="inlineStr">
         <is>
-          <t>D28 + F12·4</t>
+          <t>D30 + F12·4</t>
         </is>
       </c>
       <c r="H73" s="32" t="inlineStr">
@@ -11014,7 +11060,7 @@
       </c>
       <c r="I73" s="33" t="inlineStr">
         <is>
-          <t>D28 + F12·4</t>
+          <t>D30 + F12·4</t>
         </is>
       </c>
       <c r="J73" s="32" t="inlineStr">
@@ -11024,7 +11070,7 @@
       </c>
       <c r="K73" s="33" t="inlineStr">
         <is>
-          <t>D28 + F12·4</t>
+          <t>D30 + F12·4</t>
         </is>
       </c>
       <c r="L73" s="17" t="inlineStr">
@@ -11036,12 +11082,12 @@
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>Manija de accionamiento</t>
+          <t>Eje de palanca</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>Largo × alto (palanca)</t>
+          <t>Ø × largo</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -11049,93 +11095,123 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D74" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="E74" s="16" t="inlineStr">
-        <is>
-          <t>F11·4</t>
-        </is>
-      </c>
-      <c r="F74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="35" t="n"/>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="35" t="n"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="35" t="n"/>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="E74" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>8 × 47</t>
+        </is>
+      </c>
+      <c r="G74" s="33" t="inlineStr">
+        <is>
+          <t>D31 + F12·4</t>
+        </is>
+      </c>
+      <c r="H74" s="32" t="inlineStr">
+        <is>
+          <t>8 × 47</t>
+        </is>
+      </c>
+      <c r="I74" s="33" t="inlineStr">
+        <is>
+          <t>D31 + F12·4</t>
+        </is>
+      </c>
+      <c r="J74" s="32" t="inlineStr">
+        <is>
+          <t>8 × 47</t>
+        </is>
+      </c>
+      <c r="K74" s="33" t="inlineStr">
+        <is>
+          <t>D31 + F12·4</t>
+        </is>
+      </c>
       <c r="L74" s="17" t="inlineStr">
         <is>
-          <t>Medido a escala; cara superior a 41.5 mm del cuerpo</t>
+          <t>ABC 25 kg: Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota · ABC 50 kg, ABC 70 kg, ABC 100 kg: Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="inlineStr"/>
-      <c r="B75" s="19" t="inlineStr">
-        <is>
-          <t>Ancho de la chapa</t>
-        </is>
-      </c>
-      <c r="C75" s="20" t="inlineStr">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>Pasador de seguridad</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>Ø alambre × largo</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D75" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="E75" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="F75" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="27" t="n"/>
-      <c r="H75" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="27" t="n"/>
-      <c r="J75" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="27" t="n"/>
-      <c r="L75" s="23" t="inlineStr">
-        <is>
-          <t>No visible en la vista lateral</t>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="E75" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 53</t>
+        </is>
+      </c>
+      <c r="G75" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="H75" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 53</t>
+        </is>
+      </c>
+      <c r="I75" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="J75" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 53</t>
+        </is>
+      </c>
+      <c r="K75" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="L75" s="17" t="inlineStr">
+        <is>
+          <t>ABC 25 kg: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2) · ABC 50 kg, ABC 70 kg, ABC 100 kg: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>Manija de transporte</t>
+          <t>Manija de accionamiento</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>Tramos de la manija fija</t>
+          <t>Perfil lateral: largo × alto (x / z extremos)</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
@@ -11145,7 +11221,7 @@
       </c>
       <c r="D76" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr">
@@ -11173,7 +11249,7 @@
       <c r="K76" s="35" t="n"/>
       <c r="L76" s="17" t="inlineStr">
         <is>
-          <t>Medido a escala en el plano Fadesa</t>
+          <t>Contorno completo extraído del plano vectorial Fadesa (47 puntos), no una caja</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11257,7 @@
       <c r="A77" s="18" t="inlineStr"/>
       <c r="B77" s="19" t="inlineStr">
         <is>
-          <t>Ancho de la chapa</t>
+          <t>Ancho (chapa estampada en U)</t>
         </is>
       </c>
       <c r="C77" s="20" t="inlineStr">
@@ -11189,12 +11265,14 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D77" s="31" t="n">
-        <v>20</v>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="E77" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="F77" s="26" t="inlineStr">
@@ -11217,19 +11295,19 @@
       <c r="K77" s="27" t="n"/>
       <c r="L77" s="23" t="inlineStr">
         <is>
-          <t>No visible en la vista lateral</t>
+          <t>No visible en la vista lateral: a horcajadas del cuerpo (palanca) y de la palanca (manija)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>Eje de palanca</t>
+          <t>Manija de transporte</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>Ø × largo</t>
+          <t>Perfil lateral: largo × alto (x / z extremos)</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -11237,111 +11315,83 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D78" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="E78" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="F78" s="32" t="inlineStr">
-        <is>
-          <t>8 × 47</t>
-        </is>
-      </c>
-      <c r="G78" s="33" t="inlineStr">
-        <is>
-          <t>D29 + F12·4</t>
-        </is>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>8 × 47</t>
-        </is>
-      </c>
-      <c r="I78" s="33" t="inlineStr">
-        <is>
-          <t>D29 + F12·4</t>
-        </is>
-      </c>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>8 × 47</t>
-        </is>
-      </c>
-      <c r="K78" s="33" t="inlineStr">
-        <is>
-          <t>D29 + F12·4</t>
-        </is>
-      </c>
+      <c r="D78" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>F11·4</t>
+        </is>
+      </c>
+      <c r="F78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="35" t="n"/>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="35" t="n"/>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="35" t="n"/>
       <c r="L78" s="17" t="inlineStr">
         <is>
-          <t>ABC 25 kg: Pasa por la horquilla; sin cota en Fadesa · ABC 50 kg, ABC 70 kg, ABC 100 kg: Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
+          <t>Contorno completo extraído del plano vectorial Fadesa (37 puntos), no una caja</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="12" t="inlineStr">
-        <is>
-          <t>Pasador de seguridad</t>
-        </is>
-      </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>Ø alambre × largo</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
+      <c r="A79" s="18" t="inlineStr"/>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>Ancho (chapa estampada en U)</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D79" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="E79" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="F79" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 53</t>
-        </is>
-      </c>
-      <c r="G79" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="H79" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 53</t>
-        </is>
-      </c>
-      <c r="I79" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="J79" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 53</t>
-        </is>
-      </c>
-      <c r="K79" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="L79" s="17" t="inlineStr">
-        <is>
-          <t>ABC 25 kg: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2) · ABC 50 kg, ABC 70 kg, ABC 100 kg: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
+      <c r="D79" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E79" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="F79" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="27" t="n"/>
+      <c r="H79" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="27" t="n"/>
+      <c r="J79" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="27" t="n"/>
+      <c r="L79" s="23" t="inlineStr">
+        <is>
+          <t>No visible en la vista lateral: a horcajadas del cuerpo (palanca) y de la palanca (manija)</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11416,7 @@
       </c>
       <c r="E80" s="33" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="F80" s="41" t="n">
@@ -11374,7 +11424,7 @@
       </c>
       <c r="G80" s="33" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="H80" s="41" t="n">
@@ -11382,7 +11432,7 @@
       </c>
       <c r="I80" s="33" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="J80" s="41" t="n">
@@ -11390,7 +11440,7 @@
       </c>
       <c r="K80" s="33" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="L80" s="17" t="inlineStr">
@@ -11472,7 +11522,7 @@
       </c>
       <c r="E82" s="33" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="F82" s="32" t="inlineStr">
@@ -11482,7 +11532,7 @@
       </c>
       <c r="G82" s="33" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="H82" s="32" t="inlineStr">
@@ -11492,7 +11542,7 @@
       </c>
       <c r="I82" s="33" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="J82" s="32" t="inlineStr">
@@ -11502,7 +11552,7 @@
       </c>
       <c r="K82" s="33" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D13</t>
         </is>
       </c>
       <c r="L82" s="17" t="inlineStr">
@@ -11532,7 +11582,7 @@
       </c>
       <c r="E83" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="F83" s="41" t="n">
@@ -11540,7 +11590,7 @@
       </c>
       <c r="G83" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="H83" s="41" t="n">
@@ -11548,7 +11598,7 @@
       </c>
       <c r="I83" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="J83" s="41" t="n">
@@ -11556,7 +11606,7 @@
       </c>
       <c r="K83" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="L83" s="17" t="inlineStr">
@@ -11578,7 +11628,7 @@
         </is>
       </c>
       <c r="D84" s="21" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E84" s="24" t="inlineStr">
         <is>
@@ -11638,7 +11688,7 @@
       </c>
       <c r="E85" s="33" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="F85" s="32" t="inlineStr">
@@ -11648,7 +11698,7 @@
       </c>
       <c r="G85" s="33" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="H85" s="32" t="inlineStr">
@@ -11658,7 +11708,7 @@
       </c>
       <c r="I85" s="33" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="J85" s="32" t="inlineStr">
@@ -11668,7 +11718,7 @@
       </c>
       <c r="K85" s="33" t="inlineStr">
         <is>
-          <t>D31</t>
+          <t>D33</t>
         </is>
       </c>
       <c r="L85" s="17" t="inlineStr">
@@ -11700,7 +11750,7 @@
       </c>
       <c r="E86" s="33" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="F86" s="32" t="inlineStr">
@@ -11710,7 +11760,7 @@
       </c>
       <c r="G86" s="33" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="H86" s="32" t="inlineStr">
@@ -11720,7 +11770,7 @@
       </c>
       <c r="I86" s="33" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="J86" s="32" t="inlineStr">
@@ -11730,7 +11780,7 @@
       </c>
       <c r="K86" s="33" t="inlineStr">
         <is>
-          <t>D37</t>
+          <t>D39</t>
         </is>
       </c>
       <c r="L86" s="17" t="inlineStr">
@@ -12174,7 +12224,7 @@
       </c>
       <c r="G94" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="H94" s="32" t="inlineStr">
@@ -12184,7 +12234,7 @@
       </c>
       <c r="I94" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J94" s="32" t="inlineStr">
@@ -12194,7 +12244,7 @@
       </c>
       <c r="K94" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="L94" s="17" t="inlineStr">
@@ -12288,7 +12338,7 @@
       </c>
       <c r="E96" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="F96" s="32" t="inlineStr">
@@ -12298,7 +12348,7 @@
       </c>
       <c r="G96" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="H96" s="32" t="inlineStr">
@@ -12308,7 +12358,7 @@
       </c>
       <c r="I96" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="J96" s="32" t="inlineStr">
@@ -12318,7 +12368,7 @@
       </c>
       <c r="K96" s="33" t="inlineStr">
         <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
         </is>
       </c>
       <c r="L96" s="17" t="inlineStr">
@@ -12570,17 +12620,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId243"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId244"/>
@@ -12654,7 +12704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V113"/>
+  <dimension ref="A1:V114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -12877,7 +12927,7 @@
         </is>
       </c>
       <c r="D4" s="15" t="n">
-        <v>594.7</v>
+        <v>594.3</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -12885,7 +12935,7 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>594.7</v>
+        <v>594.3</v>
       </c>
       <c r="G4" s="16" t="inlineStr">
         <is>
@@ -12901,7 +12951,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>435.1</v>
+        <v>434.7</v>
       </c>
       <c r="K4" s="16" t="inlineStr">
         <is>
@@ -12909,7 +12959,7 @@
         </is>
       </c>
       <c r="L4" s="15" t="n">
-        <v>414.7</v>
+        <v>414.3</v>
       </c>
       <c r="M4" s="16" t="inlineStr">
         <is>
@@ -12917,7 +12967,7 @@
         </is>
       </c>
       <c r="N4" s="15" t="n">
-        <v>464.8</v>
+        <v>464.4</v>
       </c>
       <c r="O4" s="16" t="inlineStr">
         <is>
@@ -12925,7 +12975,7 @@
         </is>
       </c>
       <c r="P4" s="15" t="n">
-        <v>735</v>
+        <v>734.6</v>
       </c>
       <c r="Q4" s="16" t="inlineStr">
         <is>
@@ -12933,7 +12983,7 @@
         </is>
       </c>
       <c r="R4" s="15" t="n">
-        <v>435.1</v>
+        <v>434.7</v>
       </c>
       <c r="S4" s="16" t="inlineStr">
         <is>
@@ -12941,7 +12991,7 @@
         </is>
       </c>
       <c r="T4" s="15" t="n">
-        <v>608.1</v>
+        <v>607.7</v>
       </c>
       <c r="U4" s="16" t="inlineStr">
         <is>
@@ -12967,7 +13017,7 @@
         </is>
       </c>
       <c r="D5" s="21" t="n">
-        <v>231.2</v>
+        <v>228.3</v>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
@@ -12975,7 +13025,7 @@
         </is>
       </c>
       <c r="F5" s="21" t="n">
-        <v>241.2</v>
+        <v>238.3</v>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
@@ -12991,7 +13041,7 @@
         </is>
       </c>
       <c r="J5" s="21" t="n">
-        <v>216.7</v>
+        <v>213.7</v>
       </c>
       <c r="K5" s="22" t="inlineStr">
         <is>
@@ -12999,7 +13049,7 @@
         </is>
       </c>
       <c r="L5" s="21" t="n">
-        <v>232.2</v>
+        <v>229.3</v>
       </c>
       <c r="M5" s="22" t="inlineStr">
         <is>
@@ -13007,7 +13057,7 @@
         </is>
       </c>
       <c r="N5" s="21" t="n">
-        <v>241.2</v>
+        <v>238.3</v>
       </c>
       <c r="O5" s="22" t="inlineStr">
         <is>
@@ -13015,7 +13065,7 @@
         </is>
       </c>
       <c r="P5" s="21" t="n">
-        <v>274.2</v>
+        <v>271.3</v>
       </c>
       <c r="Q5" s="22" t="inlineStr">
         <is>
@@ -13023,7 +13073,7 @@
         </is>
       </c>
       <c r="R5" s="21" t="n">
-        <v>216.7</v>
+        <v>213.7</v>
       </c>
       <c r="S5" s="22" t="inlineStr">
         <is>
@@ -13031,7 +13081,7 @@
         </is>
       </c>
       <c r="T5" s="21" t="n">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="U5" s="22" t="inlineStr">
         <is>
@@ -13040,7 +13090,7 @@
       </c>
       <c r="V5" s="23" t="inlineStr">
         <is>
-          <t>Agua 10 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia -4 %) · AFFF 10 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia +1 %) · AFFF 50 l: Resulta del tren de rodaje IRAM 3550 (trocha 420, banda 60) (catálogo: 466; diferencia +7 %) · BC 5 kg, HCFC-HFC 5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -4 %) · Sales K 6 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 270; diferencia -14 %) · CO2 2 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 254; diferencia -5 %) · CO2 5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 310; diferencia -12 %) · Clase D 9 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia +7 %)</t>
+          <t>Agua 10 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia -5 %) · AFFF 10 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 240; diferencia -1 %) · AFFF 50 l: Resulta del tren de rodaje IRAM 3550 (trocha 420, banda 60) (catálogo: 466; diferencia +7 %) · BC 5 kg, HCFC-HFC 5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 225; diferencia -5 %) · Sales K 6 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 270; diferencia -15 %) · CO2 2 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 254; diferencia -6 %) · CO2 5 kg: Resulta de las piezas medidas en el plano Fadesa (catálogo: 310; diferencia -12 %) · Clase D 9 l: Resulta de las piezas medidas en el plano Fadesa (catálogo: 230; diferencia +5 %)</t>
         </is>
       </c>
     </row>
@@ -13237,7 +13287,7 @@
         </is>
       </c>
       <c r="D8" s="21" t="n">
-        <v>3.16</v>
+        <v>3.07</v>
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
@@ -13245,7 +13295,7 @@
         </is>
       </c>
       <c r="F8" s="21" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
@@ -13253,7 +13303,7 @@
         </is>
       </c>
       <c r="H8" s="21" t="n">
-        <v>42.66</v>
+        <v>42.6</v>
       </c>
       <c r="I8" s="24" t="inlineStr">
         <is>
@@ -13261,7 +13311,7 @@
         </is>
       </c>
       <c r="J8" s="21" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="K8" s="24" t="inlineStr">
         <is>
@@ -13269,7 +13319,7 @@
         </is>
       </c>
       <c r="L8" s="21" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="M8" s="24" t="inlineStr">
         <is>
@@ -13277,7 +13327,7 @@
         </is>
       </c>
       <c r="N8" s="21" t="n">
-        <v>6.47</v>
+        <v>6.4</v>
       </c>
       <c r="O8" s="24" t="inlineStr">
         <is>
@@ -13285,7 +13335,7 @@
         </is>
       </c>
       <c r="P8" s="21" t="n">
-        <v>14.27</v>
+        <v>14.15</v>
       </c>
       <c r="Q8" s="24" t="inlineStr">
         <is>
@@ -13293,7 +13343,7 @@
         </is>
       </c>
       <c r="R8" s="21" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="S8" s="24" t="inlineStr">
         <is>
@@ -13301,7 +13351,7 @@
         </is>
       </c>
       <c r="T8" s="21" t="n">
-        <v>6.34</v>
+        <v>6.24</v>
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
@@ -14077,7 +14127,7 @@
       </c>
       <c r="O18" s="30" t="inlineStr">
         <is>
-          <t>D33 + IRAM 2533</t>
+          <t>D35 + IRAM 2533</t>
         </is>
       </c>
       <c r="P18" s="31" t="n">
@@ -14085,7 +14135,7 @@
       </c>
       <c r="Q18" s="30" t="inlineStr">
         <is>
-          <t>D33 + IRAM 2533</t>
+          <t>D35 + IRAM 2533</t>
         </is>
       </c>
       <c r="R18" s="26" t="inlineStr">
@@ -14289,7 +14339,7 @@
       </c>
       <c r="E21" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="F21" s="31" t="n">
@@ -14297,7 +14347,7 @@
       </c>
       <c r="G21" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="H21" s="21" t="n">
@@ -14321,7 +14371,7 @@
       </c>
       <c r="M21" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="N21" s="26" t="inlineStr">
@@ -15015,7 +15065,7 @@
       </c>
       <c r="E30" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="F30" s="31" t="n">
@@ -15023,7 +15073,7 @@
       </c>
       <c r="G30" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="H30" s="21" t="n">
@@ -15047,7 +15097,7 @@
       </c>
       <c r="M30" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="N30" s="26" t="inlineStr">
@@ -15429,7 +15479,7 @@
       </c>
       <c r="E35" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="F35" s="31" t="n">
@@ -15437,7 +15487,7 @@
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="H35" s="21" t="n">
@@ -15461,7 +15511,7 @@
       </c>
       <c r="M35" s="30" t="inlineStr">
         <is>
-          <t>D09 + F28·1</t>
+          <t>D10 + F28·1</t>
         </is>
       </c>
       <c r="N35" s="26" t="inlineStr">
@@ -15985,7 +16035,7 @@
       </c>
       <c r="E42" s="33" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="F42" s="32" t="n">
@@ -15993,7 +16043,7 @@
       </c>
       <c r="G42" s="33" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="H42" s="28" t="n">
@@ -16017,7 +16067,7 @@
       </c>
       <c r="M42" s="33" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="N42" s="34" t="inlineStr">
@@ -16071,7 +16121,7 @@
       </c>
       <c r="E43" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="F43" s="31" t="n">
@@ -16079,7 +16129,7 @@
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="H43" s="25" t="n">
@@ -16103,7 +16153,7 @@
       </c>
       <c r="M43" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="N43" s="26" t="inlineStr">
@@ -16155,7 +16205,7 @@
       </c>
       <c r="E44" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
@@ -16165,7 +16215,7 @@
       </c>
       <c r="G44" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="H44" s="25" t="inlineStr">
@@ -16195,7 +16245,7 @@
       </c>
       <c r="M44" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="N44" s="26" t="inlineStr">
@@ -16253,7 +16303,7 @@
       </c>
       <c r="E45" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="F45" s="29" t="n">
@@ -16261,7 +16311,7 @@
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="H45" s="25" t="n">
@@ -16285,7 +16335,7 @@
       </c>
       <c r="M45" s="30" t="inlineStr">
         <is>
-          <t>D10</t>
+          <t>D11</t>
         </is>
       </c>
       <c r="N45" s="26" t="inlineStr">
@@ -16453,7 +16503,7 @@
       </c>
       <c r="I47" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D15</t>
+          <t>F38·6 + D17</t>
         </is>
       </c>
       <c r="J47" s="34" t="inlineStr">
@@ -16753,7 +16803,7 @@
       </c>
       <c r="I51" s="30" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D18</t>
         </is>
       </c>
       <c r="J51" s="26" t="inlineStr">
@@ -16831,7 +16881,7 @@
       </c>
       <c r="I52" s="33" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D19</t>
         </is>
       </c>
       <c r="J52" s="34" t="inlineStr">
@@ -16907,7 +16957,7 @@
       </c>
       <c r="I53" s="30" t="inlineStr">
         <is>
-          <t>D18 + F11·1</t>
+          <t>D20 + F11·1</t>
         </is>
       </c>
       <c r="J53" s="26" t="inlineStr">
@@ -16983,7 +17033,7 @@
       </c>
       <c r="I54" s="30" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D21</t>
         </is>
       </c>
       <c r="J54" s="26" t="inlineStr">
@@ -17063,7 +17113,7 @@
       </c>
       <c r="I55" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + F40·1 + D20</t>
+          <t>F38·6 + F40·1 + D22</t>
         </is>
       </c>
       <c r="J55" s="34" t="inlineStr">
@@ -17143,7 +17193,7 @@
       </c>
       <c r="I56" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D21</t>
+          <t>F38·6 + D23</t>
         </is>
       </c>
       <c r="J56" s="34" t="inlineStr">
@@ -17223,7 +17273,7 @@
       </c>
       <c r="I57" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D22</t>
+          <t>F38·6 + D24</t>
         </is>
       </c>
       <c r="J57" s="34" t="inlineStr">
@@ -17297,7 +17347,7 @@
       </c>
       <c r="I58" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D23</t>
+          <t>F38·6 + D25</t>
         </is>
       </c>
       <c r="J58" s="26" t="inlineStr">
@@ -17377,7 +17427,7 @@
       </c>
       <c r="I59" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="J59" s="34" t="inlineStr">
@@ -17527,7 +17577,7 @@
       </c>
       <c r="I61" s="30" t="inlineStr">
         <is>
-          <t>F38·6 + D24</t>
+          <t>F38·6 + D26</t>
         </is>
       </c>
       <c r="J61" s="26" t="inlineStr">
@@ -17607,7 +17657,7 @@
       </c>
       <c r="I62" s="33" t="inlineStr">
         <is>
-          <t>F38·6 + D25</t>
+          <t>F38·6 + D27</t>
         </is>
       </c>
       <c r="J62" s="34" t="inlineStr">
@@ -17685,7 +17735,7 @@
       </c>
       <c r="I63" s="33" t="inlineStr">
         <is>
-          <t>D26</t>
+          <t>D28</t>
         </is>
       </c>
       <c r="J63" s="34" t="inlineStr">
@@ -18046,7 +18096,7 @@
       </c>
       <c r="D67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="E67" s="16" t="inlineStr">
@@ -18056,7 +18106,7 @@
       </c>
       <c r="F67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="G67" s="16" t="inlineStr">
@@ -18076,7 +18126,7 @@
       </c>
       <c r="J67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="K67" s="16" t="inlineStr">
@@ -18086,7 +18136,7 @@
       </c>
       <c r="L67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="M67" s="16" t="inlineStr">
@@ -18096,7 +18146,7 @@
       </c>
       <c r="N67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="O67" s="16" t="inlineStr">
@@ -18106,7 +18156,7 @@
       </c>
       <c r="P67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="Q67" s="16" t="inlineStr">
@@ -18116,7 +18166,7 @@
       </c>
       <c r="R67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="S67" s="16" t="inlineStr">
@@ -18126,7 +18176,7 @@
       </c>
       <c r="T67" s="28" t="inlineStr">
         <is>
-          <t>38 × 12,8</t>
+          <t>36 × 12,8</t>
         </is>
       </c>
       <c r="U67" s="16" t="inlineStr">
@@ -18157,7 +18207,7 @@
       </c>
       <c r="E68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="F68" s="31" t="n">
@@ -18165,7 +18215,7 @@
       </c>
       <c r="G68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="H68" s="31" t="n">
@@ -18173,7 +18223,7 @@
       </c>
       <c r="I68" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J68" s="31" t="n">
@@ -18181,7 +18231,7 @@
       </c>
       <c r="K68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="L68" s="31" t="n">
@@ -18189,7 +18239,7 @@
       </c>
       <c r="M68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="N68" s="31" t="n">
@@ -18197,7 +18247,7 @@
       </c>
       <c r="O68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="P68" s="31" t="n">
@@ -18205,7 +18255,7 @@
       </c>
       <c r="Q68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="R68" s="31" t="n">
@@ -18213,7 +18263,7 @@
       </c>
       <c r="S68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="T68" s="31" t="n">
@@ -18221,7 +18271,7 @@
       </c>
       <c r="U68" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D09</t>
         </is>
       </c>
       <c r="V68" s="23" t="inlineStr">
@@ -18234,7 +18284,7 @@
       <c r="A69" s="18" t="inlineStr"/>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>Horquilla del pivote (alto)</t>
+          <t>Oreja del pivote: ancho / eje a (x, z)</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
@@ -18242,16 +18292,20 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D69" s="21" t="n">
-        <v>32.2</v>
+      <c r="D69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="E69" s="22" t="inlineStr">
         <is>
           <t>F09·3</t>
         </is>
       </c>
-      <c r="F69" s="21" t="n">
-        <v>32.2</v>
+      <c r="F69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="G69" s="22" t="inlineStr">
         <is>
@@ -18264,48 +18318,60 @@
         </is>
       </c>
       <c r="I69" s="27" t="n"/>
-      <c r="J69" s="21" t="n">
-        <v>32.2</v>
+      <c r="J69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="K69" s="22" t="inlineStr">
         <is>
           <t>F09·3</t>
         </is>
       </c>
-      <c r="L69" s="21" t="n">
-        <v>32.2</v>
+      <c r="L69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="M69" s="22" t="inlineStr">
         <is>
           <t>F09·3</t>
         </is>
       </c>
-      <c r="N69" s="21" t="n">
-        <v>32.2</v>
+      <c r="N69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="O69" s="22" t="inlineStr">
         <is>
           <t>F09·3</t>
         </is>
       </c>
-      <c r="P69" s="21" t="n">
-        <v>32.2</v>
+      <c r="P69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="Q69" s="22" t="inlineStr">
         <is>
           <t>F09·3</t>
         </is>
       </c>
-      <c r="R69" s="21" t="n">
-        <v>32.2</v>
+      <c r="R69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="S69" s="22" t="inlineStr">
         <is>
           <t>F09·3</t>
         </is>
       </c>
-      <c r="T69" s="21" t="n">
-        <v>32.2</v>
+      <c r="T69" s="25" t="inlineStr">
+        <is>
+          <t>22 / (-10,73; 23,79)</t>
+        </is>
       </c>
       <c r="U69" s="22" t="inlineStr">
         <is>
@@ -18314,7 +18380,7 @@
       </c>
       <c r="V69" s="23" t="inlineStr">
         <is>
-          <t>Medido a escala</t>
+          <t>Centro del agujero del pivote medido en el plano Fadesa; ancho de diseño</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18423,7 @@
       </c>
       <c r="I70" s="30" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J70" s="25" t="inlineStr">
@@ -18555,7 +18621,7 @@
       </c>
       <c r="O72" s="33" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="P72" s="32" t="inlineStr">
@@ -18565,7 +18631,7 @@
       </c>
       <c r="Q72" s="33" t="inlineStr">
         <is>
-          <t>D34</t>
+          <t>D36</t>
         </is>
       </c>
       <c r="R72" s="34" t="inlineStr">
@@ -18819,7 +18885,7 @@
       </c>
       <c r="I75" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J75" s="28" t="inlineStr">
@@ -18931,7 +18997,7 @@
       </c>
       <c r="I76" s="33" t="inlineStr">
         <is>
-          <t>D27</t>
+          <t>D29</t>
         </is>
       </c>
       <c r="J76" s="28" t="inlineStr">
@@ -19035,7 +19101,7 @@
       </c>
       <c r="I77" s="33" t="inlineStr">
         <is>
-          <t>D28 + F12·4</t>
+          <t>D30 + F12·4</t>
         </is>
       </c>
       <c r="J77" s="34" t="inlineStr">
@@ -19083,12 +19149,12 @@
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>Manija de accionamiento</t>
+          <t>Eje de palanca</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>Largo × alto (palanca)</t>
+          <t>Ø × largo</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -19096,195 +19162,223 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="E78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="F78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="G78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="H78" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I78" s="35" t="n"/>
-      <c r="J78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="K78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="L78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="M78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="N78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="O78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="P78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="Q78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="R78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="S78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
-        </is>
-      </c>
-      <c r="T78" s="28" t="inlineStr">
-        <is>
-          <t>127 × 8</t>
-        </is>
-      </c>
-      <c r="U78" s="16" t="inlineStr">
-        <is>
-          <t>F09·3</t>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="E78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="G78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="H78" s="32" t="inlineStr">
+        <is>
+          <t>8 × 47</t>
+        </is>
+      </c>
+      <c r="I78" s="33" t="inlineStr">
+        <is>
+          <t>D31 + F12·4</t>
+        </is>
+      </c>
+      <c r="J78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="K78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="L78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="M78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="N78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="O78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="P78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="Q78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="R78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="S78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
+        </is>
+      </c>
+      <c r="T78" s="32" t="inlineStr">
+        <is>
+          <t>4 × 33</t>
+        </is>
+      </c>
+      <c r="U78" s="33" t="inlineStr">
+        <is>
+          <t>D04</t>
         </is>
       </c>
       <c r="V78" s="17" t="inlineStr">
         <is>
-          <t>Medido a escala; cara superior a 41.5 mm del cuerpo</t>
+          <t>Agua 10 l, AFFF 10 l, BC 5 kg, Sales K 6 l, CO2 2 kg, CO2 5 kg, HCFC-HFC 5 kg, Clase D 9 l: Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota · AFFF 50 l: Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="inlineStr"/>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>Ancho de la chapa</t>
-        </is>
-      </c>
-      <c r="C79" s="20" t="inlineStr">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Pasador de seguridad</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>Ø alambre × largo</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="E79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="G79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="H79" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="27" t="n"/>
-      <c r="J79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="K79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="M79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="O79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="P79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="R79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="S79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="T79" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="U79" s="30" t="inlineStr">
-        <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="V79" s="23" t="inlineStr">
-        <is>
-          <t>No visible en la vista lateral</t>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="E79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="G79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 53</t>
+        </is>
+      </c>
+      <c r="I79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="K79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="L79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="M79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="N79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="O79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="P79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="Q79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="R79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="S79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="T79" s="32" t="inlineStr">
+        <is>
+          <t>3,2 × 44,5</t>
+        </is>
+      </c>
+      <c r="U79" s="33" t="inlineStr">
+        <is>
+          <t>D05 + F26·1</t>
+        </is>
+      </c>
+      <c r="V79" s="17" t="inlineStr">
+        <is>
+          <t>Agua 10 l, AFFF 10 l, BC 5 kg, Sales K 6 l, CO2 2 kg, CO2 5 kg, HCFC-HFC 5 kg, Clase D 9 l: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2) · AFFF 50 l: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>Manija de transporte</t>
+          <t>Manija de accionamiento</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>Tramos de la manija fija</t>
+          <t>Perfil lateral: largo × alto (x / z extremos)</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
@@ -19294,7 +19388,7 @@
       </c>
       <c r="D80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="E80" s="16" t="inlineStr">
@@ -19304,7 +19398,7 @@
       </c>
       <c r="F80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
@@ -19320,7 +19414,7 @@
       <c r="I80" s="35" t="n"/>
       <c r="J80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="K80" s="16" t="inlineStr">
@@ -19330,7 +19424,7 @@
       </c>
       <c r="L80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="M80" s="16" t="inlineStr">
@@ -19340,7 +19434,7 @@
       </c>
       <c r="N80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="O80" s="16" t="inlineStr">
@@ -19350,7 +19444,7 @@
       </c>
       <c r="P80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="Q80" s="16" t="inlineStr">
@@ -19360,7 +19454,7 @@
       </c>
       <c r="R80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="S80" s="16" t="inlineStr">
@@ -19370,7 +19464,7 @@
       </c>
       <c r="T80" s="28" t="inlineStr">
         <is>
-          <t>50 + 36</t>
+          <t>124,6 × 29,3 (-17,4 a 107,3 / 15,9 a 45,2)</t>
         </is>
       </c>
       <c r="U80" s="16" t="inlineStr">
@@ -19380,7 +19474,7 @@
       </c>
       <c r="V80" s="17" t="inlineStr">
         <is>
-          <t>Medido a escala en el plano Fadesa</t>
+          <t>Contorno completo extraído del plano vectorial Fadesa (47 puntos), no una caja</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19482,7 @@
       <c r="A81" s="18" t="inlineStr"/>
       <c r="B81" s="19" t="inlineStr">
         <is>
-          <t>Ancho de la chapa</t>
+          <t>Ancho (chapa estampada en U)</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr">
@@ -19396,20 +19490,24 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D81" s="31" t="n">
-        <v>20</v>
+      <c r="D81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="E81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="F81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="G81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="H81" s="26" t="inlineStr">
@@ -19418,69 +19516,81 @@
         </is>
       </c>
       <c r="I81" s="27" t="n"/>
-      <c r="J81" s="31" t="n">
-        <v>20</v>
+      <c r="J81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="K81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="L81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="M81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="N81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="O81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="P81" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="P81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="Q81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="R81" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="R81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="S81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
-        </is>
-      </c>
-      <c r="T81" s="31" t="n">
-        <v>20</v>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="T81" s="29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="U81" s="30" t="inlineStr">
         <is>
-          <t>D08</t>
+          <t>D06</t>
         </is>
       </c>
       <c r="V81" s="23" t="inlineStr">
         <is>
-          <t>No visible en la vista lateral</t>
+          <t>No visible en la vista lateral: a horcajadas del cuerpo (palanca) y de la palanca (manija)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>Eje de palanca</t>
+          <t>Manija de transporte</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>Ø × largo</t>
+          <t>Perfil lateral: largo × alto (x / z extremos)</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
@@ -19488,211 +19598,199 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="E82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="F82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="G82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="H82" s="32" t="inlineStr">
-        <is>
-          <t>8 × 47</t>
-        </is>
-      </c>
-      <c r="I82" s="33" t="inlineStr">
-        <is>
-          <t>D29 + F12·4</t>
-        </is>
-      </c>
-      <c r="J82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="K82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="L82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="M82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="N82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="O82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="P82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="Q82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="R82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="S82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
-        </is>
-      </c>
-      <c r="T82" s="32" t="inlineStr">
-        <is>
-          <t>2 × 34</t>
-        </is>
-      </c>
-      <c r="U82" s="33" t="inlineStr">
-        <is>
-          <t>D04</t>
+      <c r="D82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="F82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="35" t="n"/>
+      <c r="J82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="K82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="L82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="N82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="O82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="P82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="Q82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="R82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="S82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
+        </is>
+      </c>
+      <c r="T82" s="28" t="inlineStr">
+        <is>
+          <t>102,6 × 25,4 (1,1 a 103,7 / 4,7 a 30,1)</t>
+        </is>
+      </c>
+      <c r="U82" s="16" t="inlineStr">
+        <is>
+          <t>F09·3</t>
         </is>
       </c>
       <c r="V82" s="17" t="inlineStr">
         <is>
-          <t>Agua 10 l, AFFF 10 l, BC 5 kg, Sales K 6 l, CO2 2 kg, CO2 5 kg, HCFC-HFC 5 kg, Clase D 9 l: Pasa por la horquilla; sin cota en Fadesa · AFFF 50 l: Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
+          <t>Contorno completo extraído del plano vectorial Fadesa (37 puntos), no una caja</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>Pasador de seguridad</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="inlineStr">
-        <is>
-          <t>Ø alambre × largo</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
+      <c r="A83" s="18" t="inlineStr"/>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>Ancho (chapa estampada en U)</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="E83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="F83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="G83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="H83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 53</t>
-        </is>
-      </c>
-      <c r="I83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="J83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="K83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="L83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="M83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="N83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="O83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="P83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="Q83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="R83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="S83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="T83" s="32" t="inlineStr">
-        <is>
-          <t>3,2 × 44</t>
-        </is>
-      </c>
-      <c r="U83" s="33" t="inlineStr">
-        <is>
-          <t>D05 + F26·1</t>
-        </is>
-      </c>
-      <c r="V83" s="17" t="inlineStr">
-        <is>
-          <t>Agua 10 l, AFFF 10 l, BC 5 kg, Sales K 6 l, CO2 2 kg, CO2 5 kg, HCFC-HFC 5 kg, Clase D 9 l: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2) · AFFF 50 l: Traba con anilla Ø18 y precinto (IRAM 3550 3.4.2); cruza horquilla y nariz de la palanca</t>
+      <c r="D83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="F83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="H83" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="27" t="n"/>
+      <c r="J83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="L83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="N83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="P83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="Q83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="R83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="S83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="T83" s="29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="U83" s="30" t="inlineStr">
+        <is>
+          <t>D06</t>
+        </is>
+      </c>
+      <c r="V83" s="23" t="inlineStr">
+        <is>
+          <t>No visible en la vista lateral: a horcajadas del cuerpo (palanca) y de la palanca (manija)</t>
         </is>
       </c>
     </row>
@@ -19733,7 +19831,7 @@
       </c>
       <c r="I84" s="33" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
@@ -19757,7 +19855,7 @@
       </c>
       <c r="O84" s="33" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="P84" s="41" t="n">
@@ -19765,7 +19863,7 @@
       </c>
       <c r="Q84" s="33" t="inlineStr">
         <is>
-          <t>D30</t>
+          <t>D32</t>
         </is>
       </c>
       <c r="R84" s="15" t="n">
@@ -19933,7 +20031,7 @@
       </c>
       <c r="O86" s="33" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="P86" s="32" t="inlineStr">
@@ -19943,7 +20041,7 @@
       </c>
       <c r="Q86" s="33" t="inlineStr">
         <is>
-          <t>D35</t>
+          <t>D37</t>
         </is>
       </c>
       <c r="R86" s="34" t="inlineStr">
@@ -20012,12 +20110,12 @@
       <c r="M87" s="35" t="n"/>
       <c r="N87" s="32" t="inlineStr">
         <is>
-          <t>75,1 × 12,0 × 61,0</t>
+          <t>76,1 × 12,0 × 61,0</t>
         </is>
       </c>
       <c r="O87" s="33" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="P87" s="34" t="inlineStr">
@@ -20097,7 +20195,7 @@
       </c>
       <c r="O88" s="33" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="P88" s="32" t="inlineStr">
@@ -20107,7 +20205,7 @@
       </c>
       <c r="Q88" s="33" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="R88" s="34" t="inlineStr">
@@ -20181,7 +20279,7 @@
       </c>
       <c r="O89" s="33" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="P89" s="32" t="inlineStr">
@@ -20191,7 +20289,7 @@
       </c>
       <c r="Q89" s="33" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="R89" s="34" t="inlineStr">
@@ -20207,7 +20305,7 @@
       </c>
       <c r="U89" s="33" t="inlineStr">
         <is>
-          <t>D13</t>
+          <t>D15</t>
         </is>
       </c>
       <c r="V89" s="17" t="inlineStr">
@@ -20275,7 +20373,7 @@
       </c>
       <c r="Q90" s="33" t="inlineStr">
         <is>
-          <t>D14</t>
+          <t>D16</t>
         </is>
       </c>
       <c r="R90" s="34" t="inlineStr">
@@ -20299,12 +20397,12 @@
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>Racor de manguera</t>
+          <t>Filtro del tubo de pesca</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>Ø × largo</t>
+          <t>Envolvente L × A × H</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
@@ -20314,34 +20412,30 @@
       </c>
       <c r="D91" s="32" t="inlineStr">
         <is>
-          <t>18,0 × 12,0</t>
+          <t>24,3 × 24,3 × 25,0</t>
         </is>
       </c>
       <c r="E91" s="33" t="inlineStr">
         <is>
-          <t>D11</t>
+          <t>D12</t>
         </is>
       </c>
       <c r="F91" s="32" t="inlineStr">
         <is>
-          <t>18,0 × 12,0</t>
+          <t>24,3 × 24,3 × 25,0</t>
         </is>
       </c>
       <c r="G91" s="33" t="inlineStr">
         <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="H91" s="32" t="inlineStr">
-        <is>
-          <t>24,0 × 16,0</t>
-        </is>
-      </c>
-      <c r="I91" s="33" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="H91" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I91" s="35" t="n"/>
       <c r="J91" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -20350,396 +20444,408 @@
       <c r="K91" s="35" t="n"/>
       <c r="L91" s="32" t="inlineStr">
         <is>
+          <t>24,3 × 24,3 × 25,0</t>
+        </is>
+      </c>
+      <c r="M91" s="33" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="N91" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O91" s="35" t="n"/>
+      <c r="P91" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q91" s="35" t="n"/>
+      <c r="R91" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S91" s="35" t="n"/>
+      <c r="T91" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U91" s="35" t="n"/>
+      <c r="V91" s="17" t="inlineStr">
+        <is>
+          <t>Sólido dibujado</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Racor de manguera</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>Ø × largo</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="inlineStr">
+        <is>
           <t>18,0 × 12,0</t>
         </is>
       </c>
-      <c r="M91" s="33" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="N91" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O91" s="35" t="n"/>
-      <c r="P91" s="32" t="inlineStr">
+      <c r="E92" s="33" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="F92" s="32" t="inlineStr">
         <is>
           <t>18,0 × 12,0</t>
         </is>
       </c>
-      <c r="Q91" s="33" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="R91" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S91" s="35" t="n"/>
-      <c r="T91" s="32" t="inlineStr">
+      <c r="G92" s="33" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="H92" s="32" t="inlineStr">
+        <is>
+          <t>24,0 × 16,0</t>
+        </is>
+      </c>
+      <c r="I92" s="33" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="J92" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K92" s="35" t="n"/>
+      <c r="L92" s="32" t="inlineStr">
         <is>
           <t>18,0 × 12,0</t>
         </is>
       </c>
-      <c r="U91" s="33" t="inlineStr">
-        <is>
-          <t>D11</t>
-        </is>
-      </c>
-      <c r="V91" s="17" t="inlineStr">
+      <c r="M92" s="33" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="N92" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O92" s="35" t="n"/>
+      <c r="P92" s="32" t="inlineStr">
+        <is>
+          <t>18,0 × 12,0</t>
+        </is>
+      </c>
+      <c r="Q92" s="33" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="R92" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S92" s="35" t="n"/>
+      <c r="T92" s="32" t="inlineStr">
+        <is>
+          <t>18,0 × 12,0</t>
+        </is>
+      </c>
+      <c r="U92" s="33" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="V92" s="17" t="inlineStr">
         <is>
           <t>Sin cota en Fadesa</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="18" t="inlineStr"/>
-      <c r="B92" s="19" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="18" t="inlineStr"/>
+      <c r="B93" s="19" t="inlineStr">
         <is>
           <t>Tuerca Ø × largo / casquillo Ø × largo</t>
         </is>
       </c>
-      <c r="C92" s="20" t="inlineStr">
+      <c r="C93" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E92" s="27" t="n"/>
-      <c r="F92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="27" t="n"/>
-      <c r="H92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I92" s="27" t="n"/>
-      <c r="J92" s="25" t="inlineStr">
+      <c r="D93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="27" t="n"/>
+      <c r="F93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="27" t="n"/>
+      <c r="H93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I93" s="27" t="n"/>
+      <c r="J93" s="25" t="inlineStr">
         <is>
           <t>18,8 × 5,9 / 16,9 × 13,5</t>
         </is>
       </c>
-      <c r="K92" s="22" t="inlineStr">
+      <c r="K93" s="22" t="inlineStr">
         <is>
           <t>F09·4</t>
         </is>
       </c>
-      <c r="L92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M92" s="27" t="n"/>
-      <c r="N92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O92" s="27" t="n"/>
-      <c r="P92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q92" s="27" t="n"/>
-      <c r="R92" s="25" t="inlineStr">
+      <c r="L93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M93" s="27" t="n"/>
+      <c r="N93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O93" s="27" t="n"/>
+      <c r="P93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q93" s="27" t="n"/>
+      <c r="R93" s="25" t="inlineStr">
         <is>
           <t>18,8 × 5,9 / 16,9 × 13,5</t>
         </is>
       </c>
-      <c r="S92" s="22" t="inlineStr">
+      <c r="S93" s="22" t="inlineStr">
         <is>
           <t>F09·4</t>
         </is>
       </c>
-      <c r="T92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U92" s="27" t="n"/>
-      <c r="V92" s="23" t="inlineStr">
+      <c r="T93" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U93" s="27" t="n"/>
+      <c r="V93" s="23" t="inlineStr">
         <is>
           <t>Medido a escala en el plano Fadesa</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="12" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
         <is>
           <t>Manguera</t>
         </is>
       </c>
-      <c r="B93" s="13" t="inlineStr">
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>Ø exterior</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D93" s="41" t="n">
+      <c r="D94" s="41" t="n">
         <v>17.4</v>
       </c>
-      <c r="E93" s="33" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="F93" s="41" t="n">
+      <c r="E94" s="33" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="F94" s="41" t="n">
         <v>17.4</v>
       </c>
-      <c r="G93" s="33" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="H93" s="41" t="n">
+      <c r="G94" s="33" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="H94" s="41" t="n">
         <v>25</v>
       </c>
-      <c r="I93" s="33" t="inlineStr">
-        <is>
-          <t>D26</t>
-        </is>
-      </c>
-      <c r="J93" s="15" t="n">
+      <c r="I94" s="33" t="inlineStr">
+        <is>
+          <t>D28</t>
+        </is>
+      </c>
+      <c r="J94" s="15" t="n">
         <v>17.4</v>
       </c>
-      <c r="K93" s="16" t="inlineStr">
+      <c r="K94" s="16" t="inlineStr">
         <is>
           <t>F09·10</t>
         </is>
       </c>
-      <c r="L93" s="41" t="n">
+      <c r="L94" s="41" t="n">
         <v>17.4</v>
       </c>
-      <c r="M93" s="33" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="N93" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O93" s="35" t="n"/>
-      <c r="P93" s="41" t="n">
+      <c r="M94" s="33" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="N94" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O94" s="35" t="n"/>
+      <c r="P94" s="41" t="n">
         <v>14</v>
       </c>
-      <c r="Q93" s="33" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="R93" s="15" t="n">
+      <c r="Q94" s="33" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="R94" s="15" t="n">
         <v>17.4</v>
       </c>
-      <c r="S93" s="16" t="inlineStr">
+      <c r="S94" s="16" t="inlineStr">
         <is>
           <t>F09·10</t>
         </is>
       </c>
-      <c r="T93" s="41" t="n">
+      <c r="T94" s="41" t="n">
         <v>17.4</v>
       </c>
-      <c r="U93" s="33" t="inlineStr">
-        <is>
-          <t>D12</t>
-        </is>
-      </c>
-      <c r="V93" s="17" t="inlineStr">
+      <c r="U94" s="33" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="V94" s="17" t="inlineStr">
         <is>
           <t>Agua 10 l, AFFF 10 l, AFFF 50 l, Sales K 6 l, CO2 5 kg, Clase D 9 l: Sin cota en Fadesa · BC 5 kg, HCFC-HFC 5 kg: Medido a escala en el plano Fadesa</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="18" t="inlineStr"/>
-      <c r="B94" s="19" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="18" t="inlineStr"/>
+      <c r="B95" s="19" t="inlineStr">
         <is>
           <t>Largo desarrollado dibujado</t>
         </is>
       </c>
-      <c r="C94" s="20" t="inlineStr">
+      <c r="C95" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D94" s="21" t="n">
-        <v>419</v>
-      </c>
-      <c r="E94" s="24" t="inlineStr">
+      <c r="D95" s="21" t="n">
+        <v>420</v>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="F94" s="21" t="n">
-        <v>299</v>
-      </c>
-      <c r="G94" s="24" t="inlineStr">
+      <c r="F95" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="H94" s="21" t="n">
+      <c r="H95" s="21" t="n">
         <v>344</v>
       </c>
-      <c r="I94" s="24" t="inlineStr">
+      <c r="I95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="J94" s="21" t="n">
-        <v>278</v>
-      </c>
-      <c r="K94" s="24" t="inlineStr">
+      <c r="J95" s="21" t="n">
+        <v>279</v>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="L94" s="21" t="n">
-        <v>113</v>
-      </c>
-      <c r="M94" s="24" t="inlineStr">
+      <c r="L95" s="21" t="n">
+        <v>114</v>
+      </c>
+      <c r="M95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="N94" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O94" s="27" t="n"/>
-      <c r="P94" s="21" t="n">
-        <v>371</v>
-      </c>
-      <c r="Q94" s="24" t="inlineStr">
+      <c r="N95" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O95" s="27" t="n"/>
+      <c r="P95" s="21" t="n">
+        <v>372</v>
+      </c>
+      <c r="Q95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="R94" s="21" t="n">
-        <v>278</v>
-      </c>
-      <c r="S94" s="24" t="inlineStr">
+      <c r="R95" s="21" t="n">
+        <v>279</v>
+      </c>
+      <c r="S95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="T94" s="21" t="n">
-        <v>162</v>
-      </c>
-      <c r="U94" s="24" t="inlineStr">
+      <c r="T95" s="21" t="n">
+        <v>163</v>
+      </c>
+      <c r="U95" s="24" t="inlineStr">
         <is>
           <t>cálculo</t>
         </is>
       </c>
-      <c r="V94" s="23" t="inlineStr">
+      <c r="V95" s="23" t="inlineStr">
         <is>
           <t>Volumen del sólido / (π r²); en rodantes la manga real es la del catálogo</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>Lanza aplicadora flujo suave</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="inlineStr">
-        <is>
-          <t>Envolvente L × A × H</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E95" s="35" t="n"/>
-      <c r="F95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="35" t="n"/>
-      <c r="H95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I95" s="35" t="n"/>
-      <c r="J95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K95" s="35" t="n"/>
-      <c r="L95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M95" s="35" t="n"/>
-      <c r="N95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O95" s="35" t="n"/>
-      <c r="P95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q95" s="35" t="n"/>
-      <c r="R95" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S95" s="35" t="n"/>
-      <c r="T95" s="32" t="inlineStr">
-        <is>
-          <t>40,0 × 40,0 × 360,0</t>
-        </is>
-      </c>
-      <c r="U95" s="33" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
-      <c r="V95" s="17" t="inlineStr">
-        <is>
-          <t>Dimensiones del sólido dibujado (constantes del tipo de descarga)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>Lanza aplicadora clase K</t>
+          <t>Lanza aplicadora flujo suave</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
@@ -20776,16 +20882,12 @@
         </is>
       </c>
       <c r="K96" s="35" t="n"/>
-      <c r="L96" s="32" t="inlineStr">
-        <is>
-          <t>26,0 × 26,0 × 294,4</t>
-        </is>
-      </c>
-      <c r="M96" s="33" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
+      <c r="L96" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="35" t="n"/>
       <c r="N96" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -20804,12 +20906,16 @@
         </is>
       </c>
       <c r="S96" s="35" t="n"/>
-      <c r="T96" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U96" s="35" t="n"/>
+      <c r="T96" s="32" t="inlineStr">
+        <is>
+          <t>40,0 × 40,0 × 360,0</t>
+        </is>
+      </c>
+      <c r="U96" s="33" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="V96" s="17" t="inlineStr">
         <is>
           <t>Dimensiones del sólido dibujado (constantes del tipo de descarga)</t>
@@ -20819,12 +20925,12 @@
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>Tobera con portatobera</t>
+          <t>Lanza aplicadora clase K</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>Portatobera Ø × largo / tobera Ø × largo</t>
+          <t>Envolvente L × A × H</t>
         </is>
       </c>
       <c r="C97" s="14" t="inlineStr">
@@ -20850,22 +20956,22 @@
         </is>
       </c>
       <c r="I97" s="35" t="n"/>
-      <c r="J97" s="28" t="inlineStr">
-        <is>
-          <t>18,8 × 13,4 / 19,9 × 60,1</t>
-        </is>
-      </c>
-      <c r="K97" s="16" t="inlineStr">
-        <is>
-          <t>F09·11</t>
-        </is>
-      </c>
-      <c r="L97" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M97" s="35" t="n"/>
+      <c r="J97" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K97" s="35" t="n"/>
+      <c r="L97" s="32" t="inlineStr">
+        <is>
+          <t>26,0 × 26,0 × 294,4</t>
+        </is>
+      </c>
+      <c r="M97" s="33" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
       <c r="N97" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -20878,16 +20984,12 @@
         </is>
       </c>
       <c r="Q97" s="35" t="n"/>
-      <c r="R97" s="28" t="inlineStr">
-        <is>
-          <t>18,8 × 13,4 / 19,9 × 60,1</t>
-        </is>
-      </c>
-      <c r="S97" s="16" t="inlineStr">
-        <is>
-          <t>F09·11</t>
-        </is>
-      </c>
+      <c r="R97" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S97" s="35" t="n"/>
       <c r="T97" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -20896,19 +20998,19 @@
       <c r="U97" s="35" t="n"/>
       <c r="V97" s="17" t="inlineStr">
         <is>
-          <t>Medido a escala en el plano Fadesa</t>
+          <t>Dimensiones del sólido dibujado (constantes del tipo de descarga)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>Válvula esférica</t>
+          <t>Tobera con portatobera</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>Cuerpo × palanca</t>
+          <t>Portatobera Ø × largo / tobera Ø × largo</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -20928,22 +21030,22 @@
         </is>
       </c>
       <c r="G98" s="35" t="n"/>
-      <c r="H98" s="32" t="inlineStr">
-        <is>
-          <t>40 × 40 × 60; palanca 90</t>
-        </is>
-      </c>
-      <c r="I98" s="33" t="inlineStr">
-        <is>
-          <t>D31</t>
-        </is>
-      </c>
-      <c r="J98" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K98" s="35" t="n"/>
+      <c r="H98" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="35" t="n"/>
+      <c r="J98" s="28" t="inlineStr">
+        <is>
+          <t>18,8 × 13,4 / 19,9 × 60,1</t>
+        </is>
+      </c>
+      <c r="K98" s="16" t="inlineStr">
+        <is>
+          <t>F09·11</t>
+        </is>
+      </c>
       <c r="L98" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -20962,12 +21064,16 @@
         </is>
       </c>
       <c r="Q98" s="35" t="n"/>
-      <c r="R98" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S98" s="35" t="n"/>
+      <c r="R98" s="28" t="inlineStr">
+        <is>
+          <t>18,8 × 13,4 / 19,9 × 60,1</t>
+        </is>
+      </c>
+      <c r="S98" s="16" t="inlineStr">
+        <is>
+          <t>F09·11</t>
+        </is>
+      </c>
       <c r="T98" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -20976,19 +21082,19 @@
       <c r="U98" s="35" t="n"/>
       <c r="V98" s="17" t="inlineStr">
         <is>
-          <t>Representativa (comercial)</t>
+          <t>Medido a escala en el plano Fadesa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>Lanza espumígena</t>
+          <t>Válvula esférica</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>Envolvente L × A × H</t>
+          <t>Cuerpo × palanca</t>
         </is>
       </c>
       <c r="C99" s="14" t="inlineStr">
@@ -21002,22 +21108,22 @@
         </is>
       </c>
       <c r="E99" s="35" t="n"/>
-      <c r="F99" s="32" t="inlineStr">
-        <is>
-          <t>32,0 × 32,0 × 210,0</t>
-        </is>
-      </c>
-      <c r="G99" s="33" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
-      <c r="H99" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I99" s="35" t="n"/>
+      <c r="F99" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="35" t="n"/>
+      <c r="H99" s="32" t="inlineStr">
+        <is>
+          <t>40 × 40 × 60; palanca 90</t>
+        </is>
+      </c>
+      <c r="I99" s="33" t="inlineStr">
+        <is>
+          <t>D33</t>
+        </is>
+      </c>
       <c r="J99" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -21056,175 +21162,175 @@
       <c r="U99" s="35" t="n"/>
       <c r="V99" s="17" t="inlineStr">
         <is>
+          <t>Representativa (comercial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>Lanza espumígena</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>Envolvente L × A × H</t>
+        </is>
+      </c>
+      <c r="C100" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E100" s="35" t="n"/>
+      <c r="F100" s="32" t="inlineStr">
+        <is>
+          <t>32,0 × 32,0 × 210,0</t>
+        </is>
+      </c>
+      <c r="G100" s="33" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="H100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I100" s="35" t="n"/>
+      <c r="J100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K100" s="35" t="n"/>
+      <c r="L100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M100" s="35" t="n"/>
+      <c r="N100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O100" s="35" t="n"/>
+      <c r="P100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q100" s="35" t="n"/>
+      <c r="R100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S100" s="35" t="n"/>
+      <c r="T100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U100" s="35" t="n"/>
+      <c r="V100" s="17" t="inlineStr">
+        <is>
           <t>Dimensiones del sólido dibujado (constantes del tipo de descarga)</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="18" t="inlineStr"/>
-      <c r="B100" s="19" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr"/>
+      <c r="B101" s="19" t="inlineStr">
         <is>
           <t>Ø × largo</t>
         </is>
       </c>
-      <c r="C100" s="20" t="inlineStr">
+      <c r="C101" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E100" s="27" t="n"/>
-      <c r="F100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G100" s="27" t="n"/>
-      <c r="H100" s="29" t="inlineStr">
+      <c r="D101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E101" s="27" t="n"/>
+      <c r="F101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="27" t="n"/>
+      <c r="H101" s="29" t="inlineStr">
         <is>
           <t>40 × 380 (boca Ø56)</t>
         </is>
       </c>
-      <c r="I100" s="30" t="inlineStr">
-        <is>
-          <t>D32</t>
-        </is>
-      </c>
-      <c r="J100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K100" s="27" t="n"/>
-      <c r="L100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M100" s="27" t="n"/>
-      <c r="N100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O100" s="27" t="n"/>
-      <c r="P100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q100" s="27" t="n"/>
-      <c r="R100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S100" s="27" t="n"/>
-      <c r="T100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U100" s="27" t="n"/>
-      <c r="V100" s="23" t="inlineStr">
+      <c r="I101" s="30" t="inlineStr">
+        <is>
+          <t>D34</t>
+        </is>
+      </c>
+      <c r="J101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K101" s="27" t="n"/>
+      <c r="L101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M101" s="27" t="n"/>
+      <c r="N101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O101" s="27" t="n"/>
+      <c r="P101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q101" s="27" t="n"/>
+      <c r="R101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S101" s="27" t="n"/>
+      <c r="T101" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U101" s="27" t="n"/>
+      <c r="V101" s="23" t="inlineStr">
         <is>
           <t>Lanza espumígena de rodante</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="12" t="inlineStr">
-        <is>
-          <t>Tobera de chorro pleno</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>Ø mayor × largo</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D101" s="32" t="inlineStr">
-        <is>
-          <t>22 × 85,0</t>
-        </is>
-      </c>
-      <c r="E101" s="33" t="inlineStr">
-        <is>
-          <t>D13</t>
-        </is>
-      </c>
-      <c r="F101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G101" s="35" t="n"/>
-      <c r="H101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I101" s="35" t="n"/>
-      <c r="J101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K101" s="35" t="n"/>
-      <c r="L101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M101" s="35" t="n"/>
-      <c r="N101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O101" s="35" t="n"/>
-      <c r="P101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q101" s="35" t="n"/>
-      <c r="R101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S101" s="35" t="n"/>
-      <c r="T101" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U101" s="35" t="n"/>
-      <c r="V101" s="17" t="inlineStr">
-        <is>
-          <t>Ø de tobera por tipo; largo limitado por la altura disponible</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>Suncho portatobera</t>
+          <t>Tobera de chorro pleno</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>Fleje (alto × espesor) / Ø interior</t>
+          <t>Ø mayor × largo</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -21234,24 +21340,20 @@
       </c>
       <c r="D102" s="32" t="inlineStr">
         <is>
-          <t>18 × 1,7 / 189,6</t>
+          <t>22 × 85,0</t>
         </is>
       </c>
       <c r="E102" s="33" t="inlineStr">
         <is>
-          <t>D14</t>
-        </is>
-      </c>
-      <c r="F102" s="32" t="inlineStr">
-        <is>
-          <t>18 × 1,7 / 189,6</t>
-        </is>
-      </c>
-      <c r="G102" s="33" t="inlineStr">
-        <is>
-          <t>D14</t>
-        </is>
-      </c>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="F102" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="35" t="n"/>
       <c r="H102" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -21264,16 +21366,12 @@
         </is>
       </c>
       <c r="K102" s="35" t="n"/>
-      <c r="L102" s="32" t="inlineStr">
-        <is>
-          <t>18 × 1,7 / 189,6</t>
-        </is>
-      </c>
-      <c r="M102" s="33" t="inlineStr">
-        <is>
-          <t>D14</t>
-        </is>
-      </c>
+      <c r="L102" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M102" s="35" t="n"/>
       <c r="N102" s="34" t="inlineStr">
         <is>
           <t>—</t>
@@ -21292,301 +21390,281 @@
         </is>
       </c>
       <c r="S102" s="35" t="n"/>
-      <c r="T102" s="32" t="inlineStr">
+      <c r="T102" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U102" s="35" t="n"/>
+      <c r="V102" s="17" t="inlineStr">
+        <is>
+          <t>Ø de tobera por tipo; largo limitado por la altura disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Suncho portatobera</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="inlineStr">
+        <is>
+          <t>Fleje (alto × espesor) / Ø interior</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D103" s="32" t="inlineStr">
+        <is>
+          <t>18 × 1,7 / 189,6</t>
+        </is>
+      </c>
+      <c r="E103" s="33" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="F103" s="32" t="inlineStr">
+        <is>
+          <t>18 × 1,7 / 189,6</t>
+        </is>
+      </c>
+      <c r="G103" s="33" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="H103" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I103" s="35" t="n"/>
+      <c r="J103" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K103" s="35" t="n"/>
+      <c r="L103" s="32" t="inlineStr">
+        <is>
+          <t>18 × 1,7 / 189,6</t>
+        </is>
+      </c>
+      <c r="M103" s="33" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="N103" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O103" s="35" t="n"/>
+      <c r="P103" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q103" s="35" t="n"/>
+      <c r="R103" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S103" s="35" t="n"/>
+      <c r="T103" s="32" t="inlineStr">
         <is>
           <t>18 × 1,7 / 181,1</t>
         </is>
       </c>
-      <c r="U102" s="33" t="inlineStr">
-        <is>
-          <t>D14</t>
-        </is>
-      </c>
-      <c r="V102" s="17" t="inlineStr">
+      <c r="U103" s="33" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="V103" s="17" t="inlineStr">
         <is>
           <t>Banda de 18 mm abrazando el cuerpo</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="18" t="inlineStr"/>
-      <c r="B103" s="19" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr"/>
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t>Banda (alto) / Ø interior</t>
         </is>
       </c>
-      <c r="C103" s="20" t="inlineStr">
+      <c r="C104" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E103" s="27" t="n"/>
-      <c r="F103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G103" s="27" t="n"/>
-      <c r="H103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I103" s="27" t="n"/>
-      <c r="J103" s="25" t="inlineStr">
+      <c r="D104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" s="27" t="n"/>
+      <c r="F104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="27" t="n"/>
+      <c r="H104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I104" s="27" t="n"/>
+      <c r="J104" s="25" t="inlineStr">
         <is>
           <t>14,4 / 152,6</t>
         </is>
       </c>
-      <c r="K103" s="22" t="inlineStr">
+      <c r="K104" s="22" t="inlineStr">
         <is>
           <t>F10·12</t>
         </is>
       </c>
-      <c r="L103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M103" s="27" t="n"/>
-      <c r="N103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O103" s="27" t="n"/>
-      <c r="P103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q103" s="27" t="n"/>
-      <c r="R103" s="25" t="inlineStr">
+      <c r="L104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M104" s="27" t="n"/>
+      <c r="N104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O104" s="27" t="n"/>
+      <c r="P104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q104" s="27" t="n"/>
+      <c r="R104" s="25" t="inlineStr">
         <is>
           <t>14,4 / 152,6</t>
         </is>
       </c>
-      <c r="S103" s="22" t="inlineStr">
+      <c r="S104" s="22" t="inlineStr">
         <is>
           <t>F10·12</t>
         </is>
       </c>
-      <c r="T103" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="U103" s="27" t="n"/>
-      <c r="V103" s="23" t="inlineStr">
+      <c r="T104" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U104" s="27" t="n"/>
+      <c r="V104" s="23" t="inlineStr">
         <is>
           <t>Suncho portamanguera F674 medido a escala</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="12" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
         <is>
           <t>Etiqueta / placa de características</t>
         </is>
       </c>
-      <c r="B104" s="13" t="inlineStr">
+      <c r="B105" s="13" t="inlineStr">
         <is>
           <t>Panel central (arco 108°)</t>
         </is>
       </c>
-      <c r="C104" s="14" t="inlineStr">
+      <c r="C105" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D104" s="15" t="n">
+      <c r="D105" s="15" t="n">
         <v>179.1</v>
       </c>
-      <c r="E104" s="16" t="inlineStr">
+      <c r="E105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="F104" s="15" t="n">
+      <c r="F105" s="15" t="n">
         <v>179.1</v>
       </c>
-      <c r="G104" s="16" t="inlineStr">
+      <c r="G105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="H104" s="15" t="n">
+      <c r="H105" s="15" t="n">
         <v>301.6</v>
       </c>
-      <c r="I104" s="16" t="inlineStr">
+      <c r="I105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="J104" s="15" t="n">
+      <c r="J105" s="15" t="n">
         <v>144.2</v>
       </c>
-      <c r="K104" s="16" t="inlineStr">
+      <c r="K105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="L104" s="15" t="n">
+      <c r="L105" s="15" t="n">
         <v>179.1</v>
       </c>
-      <c r="M104" s="16" t="inlineStr">
+      <c r="M105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="N104" s="15" t="n">
+      <c r="N105" s="15" t="n">
         <v>107.4</v>
       </c>
-      <c r="O104" s="16" t="inlineStr">
+      <c r="O105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="P104" s="15" t="n">
+      <c r="P105" s="15" t="n">
         <v>131.9</v>
       </c>
-      <c r="Q104" s="16" t="inlineStr">
+      <c r="Q105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="R104" s="15" t="n">
+      <c r="R105" s="15" t="n">
         <v>144.2</v>
       </c>
-      <c r="S104" s="16" t="inlineStr">
+      <c r="S105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="T104" s="15" t="n">
+      <c r="T105" s="15" t="n">
         <v>171.1</v>
       </c>
-      <c r="U104" s="16" t="inlineStr">
+      <c r="U105" s="16" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="V104" s="17" t="inlineStr">
+      <c r="V105" s="17" t="inlineStr">
         <is>
           <t>Agua 10 l: 108° × π/180 × R(95) (cada modelo con sus valores: ver el comentario)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="18" t="inlineStr"/>
-      <c r="B105" s="19" t="inlineStr">
-        <is>
-          <t>Alas laterales (arco c/u)</t>
-        </is>
-      </c>
-      <c r="C105" s="20" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 89,5</t>
-        </is>
-      </c>
-      <c r="E105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="F105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 89,5</t>
-        </is>
-      </c>
-      <c r="G105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="H105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 150,8</t>
-        </is>
-      </c>
-      <c r="I105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="J105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 72,1</t>
-        </is>
-      </c>
-      <c r="K105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="L105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 89,5</t>
-        </is>
-      </c>
-      <c r="M105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="N105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 53,7</t>
-        </is>
-      </c>
-      <c r="O105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="P105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 66,0</t>
-        </is>
-      </c>
-      <c r="Q105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="R105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 72,1</t>
-        </is>
-      </c>
-      <c r="S105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="T105" s="36" t="inlineStr">
-        <is>
-          <t>54° = 85,5</t>
-        </is>
-      </c>
-      <c r="U105" s="37" t="inlineStr">
-        <is>
-          <t>F32·1</t>
-        </is>
-      </c>
-      <c r="V105" s="23" t="inlineStr">
-        <is>
-          <t>Relevamiento: la etiqueta envuelve ≈ 216° (72° si Ø &lt; 100)</t>
         </is>
       </c>
     </row>
@@ -21594,195 +21672,209 @@
       <c r="A106" s="18" t="inlineStr"/>
       <c r="B106" s="19" t="inlineStr">
         <is>
+          <t>Alas laterales (arco c/u)</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 89,5</t>
+        </is>
+      </c>
+      <c r="E106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="F106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 89,5</t>
+        </is>
+      </c>
+      <c r="G106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="H106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 150,8</t>
+        </is>
+      </c>
+      <c r="I106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="J106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 72,1</t>
+        </is>
+      </c>
+      <c r="K106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="L106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 89,5</t>
+        </is>
+      </c>
+      <c r="M106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="N106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 53,7</t>
+        </is>
+      </c>
+      <c r="O106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="P106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 66,0</t>
+        </is>
+      </c>
+      <c r="Q106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="R106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 72,1</t>
+        </is>
+      </c>
+      <c r="S106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="T106" s="36" t="inlineStr">
+        <is>
+          <t>54° = 85,5</t>
+        </is>
+      </c>
+      <c r="U106" s="37" t="inlineStr">
+        <is>
+          <t>F32·1</t>
+        </is>
+      </c>
+      <c r="V106" s="23" t="inlineStr">
+        <is>
+          <t>Relevamiento: la etiqueta envuelve ≈ 216° (72° si Ø &lt; 100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="inlineStr"/>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
           <t>Alto</t>
         </is>
       </c>
-      <c r="C106" s="20" t="inlineStr">
+      <c r="C107" s="20" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D106" s="21" t="n">
+      <c r="D107" s="21" t="n">
         <v>188.9</v>
       </c>
-      <c r="E106" s="22" t="inlineStr">
+      <c r="E107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="F106" s="21" t="n">
+      <c r="F107" s="21" t="n">
         <v>214.6</v>
       </c>
-      <c r="G106" s="22" t="inlineStr">
+      <c r="G107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="H106" s="21" t="n">
+      <c r="H107" s="21" t="n">
         <v>214.1</v>
       </c>
-      <c r="I106" s="22" t="inlineStr">
+      <c r="I107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="J106" s="21" t="n">
+      <c r="J107" s="21" t="n">
         <v>142</v>
       </c>
-      <c r="K106" s="22" t="inlineStr">
+      <c r="K107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="L106" s="21" t="n">
+      <c r="L107" s="21" t="n">
         <v>140</v>
       </c>
-      <c r="M106" s="22" t="inlineStr">
+      <c r="M107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="N106" s="21" t="n">
+      <c r="N107" s="21" t="n">
         <v>287.5</v>
       </c>
-      <c r="O106" s="22" t="inlineStr">
+      <c r="O107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="P106" s="21" t="n">
+      <c r="P107" s="21" t="n">
         <v>231.5</v>
       </c>
-      <c r="Q106" s="22" t="inlineStr">
+      <c r="Q107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="R106" s="21" t="n">
+      <c r="R107" s="21" t="n">
         <v>149.6</v>
       </c>
-      <c r="S106" s="22" t="inlineStr">
+      <c r="S107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="T106" s="21" t="n">
+      <c r="T107" s="21" t="n">
         <v>232.4</v>
       </c>
-      <c r="U106" s="22" t="inlineStr">
+      <c r="U107" s="22" t="inlineStr">
         <is>
           <t>F27·1</t>
         </is>
       </c>
-      <c r="V106" s="23" t="inlineStr">
+      <c r="V107" s="23" t="inlineStr">
         <is>
           <t>Alto que pide el contenido (rotulado.disposicion)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>Oblea de fabricación (PBA)</t>
-        </is>
-      </c>
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>Ø</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="E107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="F107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="G107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="H107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="J107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="K107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="L107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="M107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="N107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="O107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="P107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="R107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="S107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="T107" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="U107" s="16" t="inlineStr">
-        <is>
-          <t>F29·1</t>
-        </is>
-      </c>
-      <c r="V107" s="17" t="inlineStr">
-        <is>
-          <t>Res. OPDS 522/07 anexos 1 y 2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>Estampilla IRAM de conformidad</t>
+          <t>Oblea de fabricación (PBA)</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>Ancho × alto</t>
+          <t>Ø</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
@@ -21790,106 +21882,88 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="E108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="F108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="G108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="H108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="I108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="J108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="K108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="L108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="M108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="N108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="O108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="P108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="Q108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="R108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="S108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
-        </is>
-      </c>
-      <c r="T108" s="38" t="inlineStr">
-        <is>
-          <t>60 × 40</t>
-        </is>
-      </c>
-      <c r="U108" s="39" t="inlineStr">
-        <is>
-          <t>F30·1 + F32·2</t>
+      <c r="D108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="G108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="J108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="K108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="L108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="M108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="N108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="O108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="P108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="R108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="S108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
+        </is>
+      </c>
+      <c r="T108" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="U108" s="16" t="inlineStr">
+        <is>
+          <t>F29·1</t>
         </is>
       </c>
       <c r="V108" s="17" t="inlineStr">
         <is>
-          <t>Anexo R IRAM + relevada (a confirmar)</t>
+          <t>Res. OPDS 522/07 anexos 1 y 2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>Tarjeta de identificación AGC (CABA)</t>
+          <t>Estampilla IRAM de conformidad</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
@@ -21904,104 +21978,104 @@
       </c>
       <c r="D109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="E109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="F109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="G109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="H109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="I109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="J109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="K109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="L109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="M109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="N109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="O109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="P109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="Q109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="R109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="S109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="T109" s="38" t="inlineStr">
         <is>
-          <t>140 × 55</t>
+          <t>60 × 40</t>
         </is>
       </c>
       <c r="U109" s="39" t="inlineStr">
         <is>
-          <t>F31·1</t>
+          <t>F30·1 + F32·2</t>
         </is>
       </c>
       <c r="V109" s="17" t="inlineStr">
         <is>
-          <t>Relevada en un 10 kg (a confirmar con la AGC)</t>
+          <t>Anexo R IRAM + relevada (a confirmar)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>Etiqueta de n° de serie GS1</t>
+          <t>Tarjeta de identificación AGC (CABA)</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
@@ -22016,109 +22090,109 @@
       </c>
       <c r="D110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="E110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="F110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="G110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="H110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="I110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="J110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="K110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="L110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="M110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="N110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="O110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="P110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="Q110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="R110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="S110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="T110" s="38" t="inlineStr">
         <is>
-          <t>45 × 25</t>
+          <t>140 × 55</t>
         </is>
       </c>
       <c r="U110" s="39" t="inlineStr">
         <is>
-          <t>F33·1</t>
+          <t>F31·1</t>
         </is>
       </c>
       <c r="V110" s="17" t="inlineStr">
         <is>
-          <t>Relevada en Melisam</t>
+          <t>Relevada en un 10 kg (a confirmar con la AGC)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>Junta tórica de asiento</t>
+          <t>Etiqueta de n° de serie GS1</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>O-ring Ø ext × cordón</t>
+          <t>Ancho × alto</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
@@ -22126,111 +22200,111 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="E111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
-        </is>
-      </c>
-      <c r="F111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="G111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
-        </is>
-      </c>
-      <c r="H111" s="32" t="inlineStr">
-        <is>
-          <t>81 × 4,7</t>
-        </is>
-      </c>
-      <c r="I111" s="33" t="inlineStr">
-        <is>
-          <t>D27</t>
-        </is>
-      </c>
-      <c r="J111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="K111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
-        </is>
-      </c>
-      <c r="L111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="M111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
-        </is>
-      </c>
-      <c r="N111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="O111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
-        </is>
-      </c>
-      <c r="P111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="Q111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
-        </is>
-      </c>
-      <c r="R111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="S111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
-        </is>
-      </c>
-      <c r="T111" s="28" t="inlineStr">
-        <is>
-          <t>32,7 × 3,6</t>
-        </is>
-      </c>
-      <c r="U111" s="16" t="inlineStr">
-        <is>
-          <t>F09·6</t>
+      <c r="D111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="E111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="F111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="G111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="H111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="I111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="J111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="K111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="L111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="M111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="N111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="O111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="P111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="Q111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="R111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="S111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
+        </is>
+      </c>
+      <c r="T111" s="38" t="inlineStr">
+        <is>
+          <t>45 × 25</t>
+        </is>
+      </c>
+      <c r="U111" s="39" t="inlineStr">
+        <is>
+          <t>F33·1</t>
         </is>
       </c>
       <c r="V111" s="17" t="inlineStr">
         <is>
-          <t>Agua 10 l, AFFF 10 l, BC 5 kg, Sales K 6 l, CO2 2 kg, CO2 5 kg, HCFC-HFC 5 kg, Clase D 9 l: Medido a escala en el plano Fadesa · AFFF 50 l: Interno: no se ve en el plano Fadesa (G763)</t>
+          <t>Relevada en Melisam</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>Faja de garantía válvula-cuello</t>
+          <t>Junta tórica de asiento</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>Ancho × alto</t>
+          <t>O-ring Ø ext × cordón</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -22238,216 +22312,328 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="D112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="E112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="F112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="G112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="H112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="I112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="J112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="K112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="L112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="M112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="N112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="O112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="P112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="Q112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="R112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="S112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
-        </is>
-      </c>
-      <c r="T112" s="38" t="inlineStr">
-        <is>
-          <t>30 × 40</t>
-        </is>
-      </c>
-      <c r="U112" s="39" t="inlineStr">
-        <is>
-          <t>F34·1</t>
+      <c r="D112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
+        </is>
+      </c>
+      <c r="F112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="G112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
+        </is>
+      </c>
+      <c r="H112" s="32" t="inlineStr">
+        <is>
+          <t>81 × 4,7</t>
+        </is>
+      </c>
+      <c r="I112" s="33" t="inlineStr">
+        <is>
+          <t>D29</t>
+        </is>
+      </c>
+      <c r="J112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="K112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
+        </is>
+      </c>
+      <c r="L112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="M112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
+        </is>
+      </c>
+      <c r="N112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="O112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
+        </is>
+      </c>
+      <c r="P112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="Q112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
+        </is>
+      </c>
+      <c r="R112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="S112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
+        </is>
+      </c>
+      <c r="T112" s="28" t="inlineStr">
+        <is>
+          <t>32,7 × 3,6</t>
+        </is>
+      </c>
+      <c r="U112" s="16" t="inlineStr">
+        <is>
+          <t>F09·6</t>
         </is>
       </c>
       <c r="V112" s="17" t="inlineStr">
         <is>
-          <t>Relevada en la línea Georgia</t>
+          <t>Agua 10 l, AFFF 10 l, BC 5 kg, Sales K 6 l, CO2 2 kg, CO2 5 kg, HCFC-HFC 5 kg, Clase D 9 l: Medido a escala en el plano Fadesa · AFFF 50 l: Interno: no se ve en el plano Fadesa (G763)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
+          <t>Faja de garantía válvula-cuello</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>Ancho × alto</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="E113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="F113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="G113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="H113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="I113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="J113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="K113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="L113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="M113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="N113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="O113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="P113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="Q113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="R113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="S113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="T113" s="38" t="inlineStr">
+        <is>
+          <t>30 × 40</t>
+        </is>
+      </c>
+      <c r="U113" s="39" t="inlineStr">
+        <is>
+          <t>F34·1</t>
+        </is>
+      </c>
+      <c r="V113" s="17" t="inlineStr">
+        <is>
+          <t>Relevada en la línea Georgia</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
           <t>Precinto de fábrica</t>
         </is>
       </c>
-      <c r="B113" s="13" t="inlineStr">
+      <c r="B114" s="13" t="inlineStr">
         <is>
           <t>Ø × largo</t>
         </is>
       </c>
-      <c r="C113" s="14" t="inlineStr">
+      <c r="C114" s="14" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="D113" s="32" t="inlineStr">
+      <c r="D114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="E113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="F113" s="32" t="inlineStr">
+      <c r="E114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="F114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="G113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="H113" s="32" t="inlineStr">
+      <c r="G114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="H114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="I113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="J113" s="32" t="inlineStr">
+      <c r="I114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="J114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="K113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="L113" s="32" t="inlineStr">
+      <c r="K114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="L114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="M113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="N113" s="32" t="inlineStr">
+      <c r="M114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="N114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="O113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="P113" s="32" t="inlineStr">
+      <c r="O114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="P114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="Q113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="R113" s="32" t="inlineStr">
+      <c r="Q114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="R114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="S113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="T113" s="32" t="inlineStr">
+      <c r="S114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="T114" s="32" t="inlineStr">
         <is>
           <t>5 × 10</t>
         </is>
       </c>
-      <c r="U113" s="33" t="inlineStr">
-        <is>
-          <t>D07 + IRAM 3517-2 9.4.13</t>
-        </is>
-      </c>
-      <c r="V113" s="17" t="inlineStr">
+      <c r="U114" s="33" t="inlineStr">
+        <is>
+          <t>D08 + IRAM 3517-2 9.4.13</t>
+        </is>
+      </c>
+      <c r="V114" s="17" t="inlineStr">
         <is>
           <t>IRAM 3517-2 9.4.13 (precinto con id. del fabricante)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:V113"/>
+  <autoFilter ref="A3:V114"/>
   <mergeCells count="13">
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="F2:G2"/>
@@ -22759,48 +22945,48 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId293"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId294"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U78" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U79" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U80" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U81" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U82" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q78" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S78" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U78" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q79" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S79" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U79" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O80" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q80" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S80" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U80" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O81" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q81" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S81" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U81" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K82" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O82" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q82" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S82" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U82" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId337"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K83" r:id="rId338"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId339"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId340"/>
@@ -22827,124 +23013,127 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q90" r:id="rId361"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId362"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q91" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U91" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S92" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M93" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q93" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U93" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U95" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M96" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S97" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M102" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U102" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S103" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M104" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q104" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U104" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q105" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U105" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q106" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U106" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q107" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U107" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q108" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U108" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q109" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q110" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U110" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q111" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U111" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q112" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U112" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q113" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U113" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M91" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M92" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q92" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U92" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S93" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M94" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q94" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S94" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U94" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U96" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M97" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S98" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M103" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U103" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S104" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M105" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q105" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S105" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U105" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M106" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q106" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S106" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U106" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K107" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O107" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q107" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S107" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U107" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M108" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O108" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q108" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S108" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U108" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M109" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q109" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S109" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U109" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M110" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q110" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S110" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U110" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M111" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q111" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S111" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U111" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M112" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q112" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S112" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U112" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M113" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q113" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S113" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U113" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K114" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M114" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q114" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S114" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U114" r:id="rId484"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -22958,7 +23147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -23925,7 +24114,7 @@
     <row r="44">
       <c r="A44" s="42" t="inlineStr">
         <is>
-          <t>Valores de diseño FLAMA (amarillo/naranja en las matrices). Links al commit 2a50ed5.</t>
+          <t>Valores de diseño FLAMA (amarillo/naranja en las matrices). Links al commit 9cf9127.</t>
         </is>
       </c>
     </row>
@@ -23964,7 +24153,7 @@
       </c>
       <c r="B46" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 228</t>
+          <t>flama/modelo3d.py línea 231</t>
         </is>
       </c>
       <c r="C46" s="45" t="inlineStr">
@@ -23991,12 +24180,12 @@
       </c>
       <c r="B47" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 282</t>
+          <t>flama/modelo3d.py línea 285</t>
         </is>
       </c>
       <c r="C47" s="45" t="inlineStr">
         <is>
-          <t>Cuerpo de válvula: Fondo del cuerpo; Cuerpo de válvula: Salida a la manguera Ø × largo; Manija de accionamiento: Ancho de la chapa; Manija de transporte: Ancho de la chapa</t>
+          <t>Cuerpo de válvula: Fondo del cuerpo; Cuerpo de válvula: Salida a la manguera Ø × largo</t>
         </is>
       </c>
       <c r="D47" s="45" t="inlineStr">
@@ -24018,7 +24207,7 @@
       </c>
       <c r="B48" s="44" t="inlineStr">
         <is>
-          <t>flama/bom.py línea 220</t>
+          <t>flama/bom.py línea 221</t>
         </is>
       </c>
       <c r="C48" s="45" t="inlineStr">
@@ -24045,7 +24234,7 @@
       </c>
       <c r="B49" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 384</t>
+          <t>flama/modelo3d.py línea 424</t>
         </is>
       </c>
       <c r="C49" s="45" t="inlineStr">
@@ -24055,7 +24244,7 @@
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>Pasa por la horquilla; sin cota en Fadesa</t>
+          <t>Pasa por la oreja y la palanca en el agujero del plano Fadesa; Ø sin cota</t>
         </is>
       </c>
       <c r="E49" s="45" t="inlineStr">
@@ -24072,7 +24261,7 @@
       </c>
       <c r="B50" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 387</t>
+          <t>flama/modelo3d.py línea 407</t>
         </is>
       </c>
       <c r="C50" s="45" t="inlineStr">
@@ -24099,22 +24288,22 @@
       </c>
       <c r="B51" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 464</t>
+          <t>flama/modelo3d.py línea 418</t>
         </is>
       </c>
       <c r="C51" s="45" t="inlineStr">
         <is>
-          <t>Tobera: Boquilla Ø base / Ø punta × largo</t>
+          <t>Manija de accionamiento: Ancho (chapa estampada en U); Manija de transporte: Ancho (chapa estampada en U)</t>
         </is>
       </c>
       <c r="D51" s="45" t="inlineStr">
         <is>
-          <t>F510: el plano Fadesa no muestra tobera aparte</t>
+          <t>No visible en la vista lateral: a horcajadas del cuerpo (palanca) y de la palanca (manija)</t>
         </is>
       </c>
       <c r="E51" s="45" t="inlineStr">
         <is>
-          <t>ABC 1 kg</t>
+          <t>13 modelos</t>
         </is>
       </c>
     </row>
@@ -24126,22 +24315,22 @@
       </c>
       <c r="B52" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 823</t>
+          <t>flama/modelo3d.py línea 492</t>
         </is>
       </c>
       <c r="C52" s="45" t="inlineStr">
         <is>
-          <t>Precinto de fábrica: Ø × largo</t>
+          <t>Tobera: Boquilla Ø base / Ø punta × largo</t>
         </is>
       </c>
       <c r="D52" s="45" t="inlineStr">
         <is>
-          <t>IRAM 3517-2 9.4.13 (precinto con id. del fabricante)</t>
+          <t>F510: el plano Fadesa no muestra tobera aparte</t>
         </is>
       </c>
       <c r="E52" s="45" t="inlineStr">
         <is>
-          <t>los 17</t>
+          <t>ABC 1 kg</t>
         </is>
       </c>
     </row>
@@ -24153,22 +24342,22 @@
       </c>
       <c r="B53" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 286</t>
+          <t>flama/modelo3d.py línea 851</t>
         </is>
       </c>
       <c r="C53" s="45" t="inlineStr">
         <is>
-          <t>Cuerpo de válvula: Fondo del cuerpo; Manija de accionamiento: Ancho de la chapa; Manija de transporte: Ancho de la chapa</t>
+          <t>Precinto de fábrica: Ø × largo</t>
         </is>
       </c>
       <c r="D53" s="45" t="inlineStr">
         <is>
-          <t>No visible en la vista lateral Fadesa</t>
+          <t>IRAM 3517-2 9.4.13 (precinto con id. del fabricante)</t>
         </is>
       </c>
       <c r="E53" s="45" t="inlineStr">
         <is>
-          <t>12 modelos</t>
+          <t>los 17</t>
         </is>
       </c>
     </row>
@@ -24180,22 +24369,22 @@
       </c>
       <c r="B54" s="44" t="inlineStr">
         <is>
-          <t>flama/catalogo.py línea 120</t>
+          <t>flama/modelo3d.py línea 289</t>
         </is>
       </c>
       <c r="C54" s="45" t="inlineStr">
         <is>
-          <t>Cuerpo (virola): Espesor; Cúpula: Espesor; Fondo: Espesor</t>
+          <t>Cuerpo de válvula: Fondo del cuerpo</t>
         </is>
       </c>
       <c r="D54" s="45" t="inlineStr">
         <is>
-          <t>Inox 0,8 (≥ 0,63 mín. IRAM 3525 3.2.1 b)</t>
+          <t>No visible en la vista lateral Fadesa</t>
         </is>
       </c>
       <c r="E54" s="45" t="inlineStr">
         <is>
-          <t>AFFF 10 l, Agua 10 l, Sales K 6 l</t>
+          <t>12 modelos</t>
         </is>
       </c>
     </row>
@@ -24207,17 +24396,17 @@
       </c>
       <c r="B55" s="44" t="inlineStr">
         <is>
-          <t>flama/catalogo.py línea 81</t>
+          <t>flama/catalogo.py línea 120</t>
         </is>
       </c>
       <c r="C55" s="45" t="inlineStr">
         <is>
-          <t>Cuello roscado: Ø exterior; Cuello roscado: Altura sobre la cúpula; Cuello roscado: Rosca; Cuello roscado: Ø del asiento</t>
+          <t>Cuerpo (virola): Espesor; Cúpula: Espesor; Fondo: Espesor</t>
         </is>
       </c>
       <c r="D55" s="45" t="inlineStr">
         <is>
-          <t>Supuesto de diseño</t>
+          <t>Inox 0,8 (≥ 0,63 mín. IRAM 3525 3.2.1 b)</t>
         </is>
       </c>
       <c r="E55" s="45" t="inlineStr">
@@ -24234,22 +24423,22 @@
       </c>
       <c r="B56" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 492</t>
+          <t>flama/catalogo.py línea 81</t>
         </is>
       </c>
       <c r="C56" s="45" t="inlineStr">
         <is>
-          <t>Racor de manguera: Ø × largo</t>
+          <t>Cuello roscado: Ø exterior; Cuello roscado: Altura sobre la cúpula; Cuello roscado: Rosca; Cuello roscado: Ø del asiento</t>
         </is>
       </c>
       <c r="D56" s="45" t="inlineStr">
         <is>
-          <t>Sin cota en Fadesa</t>
+          <t>Supuesto de diseño</t>
         </is>
       </c>
       <c r="E56" s="45" t="inlineStr">
         <is>
-          <t>10 modelos</t>
+          <t>AFFF 10 l, Agua 10 l, Sales K 6 l</t>
         </is>
       </c>
     </row>
@@ -24261,22 +24450,22 @@
       </c>
       <c r="B57" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 433</t>
+          <t>flama/modelo3d.py línea 445</t>
         </is>
       </c>
       <c r="C57" s="45" t="inlineStr">
         <is>
-          <t>Manguera: Ø exterior</t>
+          <t>Filtro del tubo de pesca: Envolvente L × A × H</t>
         </is>
       </c>
       <c r="D57" s="45" t="inlineStr">
         <is>
-          <t>Sin cota en Fadesa</t>
+          <t>Sólido dibujado</t>
         </is>
       </c>
       <c r="E57" s="45" t="inlineStr">
         <is>
-          <t>5 modelos</t>
+          <t>AFFF 10 l, Agua 10 l, Sales K 6 l</t>
         </is>
       </c>
     </row>
@@ -24288,22 +24477,22 @@
       </c>
       <c r="B58" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 434</t>
+          <t>flama/modelo3d.py línea 520</t>
         </is>
       </c>
       <c r="C58" s="45" t="inlineStr">
         <is>
-          <t>Tobera de chorro pleno: Ø mayor × largo; Lanza espumígena: Envolvente L × A × H; Lanza aplicadora clase K: Envolvente L × A × H; Brazo giratorio: Envolvente L × A × H (+3)</t>
+          <t>Racor de manguera: Ø × largo</t>
         </is>
       </c>
       <c r="D58" s="45" t="inlineStr">
         <is>
-          <t>Ø de tobera por tipo; largo limitado por la altura disponible</t>
+          <t>Sin cota en Fadesa</t>
         </is>
       </c>
       <c r="E58" s="45" t="inlineStr">
         <is>
-          <t>6 modelos</t>
+          <t>10 modelos</t>
         </is>
       </c>
     </row>
@@ -24315,17 +24504,17 @@
       </c>
       <c r="B59" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 544</t>
+          <t>flama/modelo3d.py línea 458</t>
         </is>
       </c>
       <c r="C59" s="45" t="inlineStr">
         <is>
-          <t>Suncho portatobera: Fleje (alto × espesor) / Ø interior; Suncho soporte de difusor: Fleje (alto × espesor) / Ø interior</t>
+          <t>Manguera: Ø exterior</t>
         </is>
       </c>
       <c r="D59" s="45" t="inlineStr">
         <is>
-          <t>Banda de 18 mm abrazando el cuerpo</t>
+          <t>Sin cota en Fadesa</t>
         </is>
       </c>
       <c r="E59" s="45" t="inlineStr">
@@ -24342,22 +24531,22 @@
       </c>
       <c r="B60" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 573</t>
+          <t>flama/modelo3d.py línea 459</t>
         </is>
       </c>
       <c r="C60" s="45" t="inlineStr">
         <is>
-          <t>Tercera pata: Ancho × pie × e</t>
+          <t>Tobera de chorro pleno: Ø mayor × largo; Lanza espumígena: Envolvente L × A × H; Lanza aplicadora clase K: Envolvente L × A × H; Brazo giratorio: Envolvente L × A × H (+3)</t>
         </is>
       </c>
       <c r="D60" s="45" t="inlineStr">
         <is>
-          <t>Chapa plegada en L, adelante a 0,75·R del eje, soldada al casquete inferior</t>
+          <t>Ø de tobera por tipo; largo limitado por la altura disponible</t>
         </is>
       </c>
       <c r="E60" s="45" t="inlineStr">
         <is>
-          <t>5 modelos</t>
+          <t>6 modelos</t>
         </is>
       </c>
     </row>
@@ -24369,17 +24558,17 @@
       </c>
       <c r="B61" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 608</t>
+          <t>flama/modelo3d.py línea 572</t>
         </is>
       </c>
       <c r="C61" s="45" t="inlineStr">
         <is>
-          <t>Neumático macizo: Ø interior del macizo; Rueda con cubierta neumática: Ø interior del macizo</t>
+          <t>Suncho portatobera: Fleje (alto × espesor) / Ø interior; Suncho soporte de difusor: Fleje (alto × espesor) / Ø interior</t>
         </is>
       </c>
       <c r="D61" s="45" t="inlineStr">
         <is>
-          <t>0,72 × Ø rueda</t>
+          <t>Banda de 18 mm abrazando el cuerpo</t>
         </is>
       </c>
       <c r="E61" s="45" t="inlineStr">
@@ -24396,17 +24585,17 @@
       </c>
       <c r="B62" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 610</t>
+          <t>flama/modelo3d.py línea 601</t>
         </is>
       </c>
       <c r="C62" s="45" t="inlineStr">
         <is>
-          <t>Llanta con cubo: Ø de la llanta</t>
+          <t>Tercera pata: Ancho × pie × e</t>
         </is>
       </c>
       <c r="D62" s="45" t="inlineStr">
         <is>
-          <t>0,72 × Ø rueda</t>
+          <t>Chapa plegada en L, adelante a 0,75·R del eje, soldada al casquete inferior</t>
         </is>
       </c>
       <c r="E62" s="45" t="inlineStr">
@@ -24423,17 +24612,17 @@
       </c>
       <c r="B63" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 609</t>
+          <t>flama/modelo3d.py línea 636</t>
         </is>
       </c>
       <c r="C63" s="45" t="inlineStr">
         <is>
-          <t>Llanta con cubo: Espesor aro / disco</t>
+          <t>Neumático macizo: Ø interior del macizo; Rueda con cubierta neumática: Ø interior del macizo</t>
         </is>
       </c>
       <c r="D63" s="45" t="inlineStr">
         <is>
-          <t>Chapa estampada; ajustado a la masa de los planos Fadesa</t>
+          <t>0,72 × Ø rueda</t>
         </is>
       </c>
       <c r="E63" s="45" t="inlineStr">
@@ -24450,17 +24639,17 @@
       </c>
       <c r="B64" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 612</t>
+          <t>flama/modelo3d.py línea 638</t>
         </is>
       </c>
       <c r="C64" s="45" t="inlineStr">
         <is>
-          <t>Llanta con cubo: Cubo Ø ext / Ø int</t>
+          <t>Llanta con cubo: Ø de la llanta</t>
         </is>
       </c>
       <c r="D64" s="45" t="inlineStr">
         <is>
-          <t>Cubo para eje Ø25</t>
+          <t>0,72 × Ø rueda</t>
         </is>
       </c>
       <c r="E64" s="45" t="inlineStr">
@@ -24477,17 +24666,17 @@
       </c>
       <c r="B65" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 602</t>
+          <t>flama/modelo3d.py línea 637</t>
         </is>
       </c>
       <c r="C65" s="45" t="inlineStr">
         <is>
-          <t>Eje de ruedas: Ø × largo / posición</t>
+          <t>Llanta con cubo: Espesor aro / disco</t>
         </is>
       </c>
       <c r="D65" s="45" t="inlineStr">
         <is>
-          <t>Barra SAE 1045 Ø25 comprada; recta, detrás de la pared trasera (luz 15) a la altura del centro de rueda; largo = trocha + banda + arandelas</t>
+          <t>Chapa estampada; ajustado a la masa de los planos Fadesa</t>
         </is>
       </c>
       <c r="E65" s="45" t="inlineStr">
@@ -24504,17 +24693,17 @@
       </c>
       <c r="B66" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 570</t>
+          <t>flama/modelo3d.py línea 640</t>
         </is>
       </c>
       <c r="C66" s="45" t="inlineStr">
         <is>
-          <t>Arandelas de tope (4): Ø ext × Ø int × e (4 u)</t>
+          <t>Llanta con cubo: Cubo Ø ext / Ø int</t>
         </is>
       </c>
       <c r="D66" s="45" t="inlineStr">
         <is>
-          <t>El proceso las compra; medidas de diseño</t>
+          <t>Cubo para eje Ø25</t>
         </is>
       </c>
       <c r="E66" s="45" t="inlineStr">
@@ -24531,17 +24720,17 @@
       </c>
       <c r="B67" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 567</t>
+          <t>flama/modelo3d.py línea 630</t>
         </is>
       </c>
       <c r="C67" s="45" t="inlineStr">
         <is>
-          <t>Soportes del eje (2): Alto × largo × e (2 u)</t>
+          <t>Eje de ruedas: Ø × largo / posición</t>
         </is>
       </c>
       <c r="D67" s="45" t="inlineStr">
         <is>
-          <t>Chapa de orilla soldada atrás y abajo; desde la pared hasta 25 mm detrás del eje</t>
+          <t>Barra SAE 1045 Ø25 comprada; recta, detrás de la pared trasera (luz 15) a la altura del centro de rueda; largo = trocha + banda + arandelas</t>
         </is>
       </c>
       <c r="E67" s="45" t="inlineStr">
@@ -24558,17 +24747,17 @@
       </c>
       <c r="B68" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 568</t>
+          <t>flama/modelo3d.py línea 598</t>
         </is>
       </c>
       <c r="C68" s="45" t="inlineStr">
         <is>
-          <t>Soportes del eje (2): Separación de los soportes</t>
+          <t>Arandelas de tope (4): Ø ext × Ø int × e (4 u)</t>
         </is>
       </c>
       <c r="D68" s="45" t="inlineStr">
         <is>
-          <t>± 0,55·R</t>
+          <t>El proceso las compra; medidas de diseño</t>
         </is>
       </c>
       <c r="E68" s="45" t="inlineStr">
@@ -24585,17 +24774,17 @@
       </c>
       <c r="B69" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 571</t>
+          <t>flama/modelo3d.py línea 595</t>
         </is>
       </c>
       <c r="C69" s="45" t="inlineStr">
         <is>
-          <t>Manija del carro: Caño; Manija del carro: Separación de las patas (ejes) / largo desarrollado</t>
+          <t>Soportes del eje (2): Alto × largo × e (2 u)</t>
         </is>
       </c>
       <c r="D69" s="45" t="inlineStr">
         <is>
-          <t>El proceso compra el caño de la manija</t>
+          <t>Chapa de orilla soldada atrás y abajo; desde la pared hasta 25 mm detrás del eje</t>
         </is>
       </c>
       <c r="E69" s="45" t="inlineStr">
@@ -24612,17 +24801,17 @@
       </c>
       <c r="B70" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 572</t>
+          <t>flama/modelo3d.py línea 596</t>
         </is>
       </c>
       <c r="C70" s="45" t="inlineStr">
         <is>
-          <t>Ganchos portamanguera (2): Ancho × vuelo × labio × e (2 u)</t>
+          <t>Soportes del eje (2): Separación de los soportes</t>
         </is>
       </c>
       <c r="D70" s="45" t="inlineStr">
         <is>
-          <t>Costado de la salida, arriba (12 %) y abajo (90 %) del cuerpo; vuelo = 2 Ø de manga + 10</t>
+          <t>± 0,55·R</t>
         </is>
       </c>
       <c r="E70" s="45" t="inlineStr">
@@ -24639,17 +24828,17 @@
       </c>
       <c r="B71" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 590</t>
+          <t>flama/modelo3d.py línea 599</t>
         </is>
       </c>
       <c r="C71" s="45" t="inlineStr">
         <is>
-          <t>Manguera (tramo enrollado): Ø exterior; Manguera: Ø exterior</t>
+          <t>Manija del carro: Caño; Manija del carro: Separación de las patas (ejes) / largo desarrollado</t>
         </is>
       </c>
       <c r="D71" s="45" t="inlineStr">
         <is>
-          <t>Sin cota en Fadesa</t>
+          <t>El proceso compra el caño de la manija</t>
         </is>
       </c>
       <c r="E71" s="45" t="inlineStr">
@@ -24666,22 +24855,22 @@
       </c>
       <c r="B72" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 290</t>
+          <t>flama/modelo3d.py línea 600</t>
         </is>
       </c>
       <c r="C72" s="45" t="inlineStr">
         <is>
-          <t>Cuerpo de válvula: Fondo del cuerpo; Cuerpo de válvula: Salida a la manguera Ø × largo; Vástago: Vástago Ø × largo / asiento Ø; Resorte de válvula: Resorte Ø × largo libre (+1)</t>
+          <t>Ganchos portamanguera (2): Ancho × vuelo × labio × e (2 u)</t>
         </is>
       </c>
       <c r="D72" s="45" t="inlineStr">
         <is>
-          <t>No visible en la vista lateral Fadesa</t>
+          <t>Costado de la salida, arriba (12 %) y abajo (90 %) del cuerpo; vuelo = 2 Ø de manga + 10</t>
         </is>
       </c>
       <c r="E72" s="45" t="inlineStr">
         <is>
-          <t>4 modelos</t>
+          <t>5 modelos</t>
         </is>
       </c>
     </row>
@@ -24693,22 +24882,22 @@
       </c>
       <c r="B73" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 374</t>
+          <t>flama/modelo3d.py línea 618</t>
         </is>
       </c>
       <c r="C73" s="45" t="inlineStr">
         <is>
-          <t>Palanca de accionamiento: Palanca largo × alto × espesor / empuñadura</t>
+          <t>Manguera (tramo enrollado): Ø exterior; Manguera: Ø exterior</t>
         </is>
       </c>
       <c r="D73" s="45" t="inlineStr">
         <is>
-          <t>Gira en la ranura de la horquilla (eje según X, plano Fadesa); hacia atrás, 0,75·R con 15 de luz a la manija del carro; sin cota en Fadesa</t>
+          <t>Sin cota en Fadesa</t>
         </is>
       </c>
       <c r="E73" s="45" t="inlineStr">
         <is>
-          <t>4 modelos</t>
+          <t>5 modelos</t>
         </is>
       </c>
     </row>
@@ -24720,17 +24909,17 @@
       </c>
       <c r="B74" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 383</t>
+          <t>flama/modelo3d.py línea 293</t>
         </is>
       </c>
       <c r="C74" s="45" t="inlineStr">
         <is>
-          <t>Eje de palanca: Ø × largo</t>
+          <t>Cuerpo de válvula: Fondo del cuerpo; Cuerpo de válvula: Salida a la manguera Ø × largo; Vástago: Vástago Ø × largo / asiento Ø; Resorte de válvula: Resorte Ø × largo libre (+1)</t>
         </is>
       </c>
       <c r="D74" s="45" t="inlineStr">
         <is>
-          <t>Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
+          <t>No visible en la vista lateral Fadesa</t>
         </is>
       </c>
       <c r="E74" s="45" t="inlineStr">
@@ -24747,22 +24936,22 @@
       </c>
       <c r="B75" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 453</t>
+          <t>flama/modelo3d.py línea 394</t>
         </is>
       </c>
       <c r="C75" s="45" t="inlineStr">
         <is>
-          <t>Caño de pesca (sifón): Ø exterior</t>
+          <t>Palanca de accionamiento: Palanca largo × alto × espesor / empuñadura</t>
         </is>
       </c>
       <c r="D75" s="45" t="inlineStr">
         <is>
-          <t>Sin cota en Fadesa</t>
+          <t>Gira en la ranura de la horquilla (eje según X, plano Fadesa); hacia atrás, 0,75·R con 15 de luz a la manija del carro; sin cota en Fadesa</t>
         </is>
       </c>
       <c r="E75" s="45" t="inlineStr">
         <is>
-          <t>7 modelos</t>
+          <t>4 modelos</t>
         </is>
       </c>
     </row>
@@ -24774,22 +24963,22 @@
       </c>
       <c r="B76" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 689</t>
+          <t>flama/modelo3d.py línea 403</t>
         </is>
       </c>
       <c r="C76" s="45" t="inlineStr">
         <is>
-          <t>Válvula esférica: Cuerpo × palanca</t>
+          <t>Eje de palanca: Ø × largo</t>
         </is>
       </c>
       <c r="D76" s="45" t="inlineStr">
         <is>
-          <t>Representativa (comercial)</t>
+          <t>Tornillo F840 + buje + arandela del plano Fadesa, sin cota</t>
         </is>
       </c>
       <c r="E76" s="45" t="inlineStr">
         <is>
-          <t>5 modelos</t>
+          <t>4 modelos</t>
         </is>
       </c>
     </row>
@@ -24801,22 +24990,22 @@
       </c>
       <c r="B77" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 694</t>
+          <t>flama/modelo3d.py línea 478</t>
         </is>
       </c>
       <c r="C77" s="45" t="inlineStr">
         <is>
-          <t>Lanza espumígena: Ø × largo</t>
+          <t>Caño de pesca (sifón): Ø exterior</t>
         </is>
       </c>
       <c r="D77" s="45" t="inlineStr">
         <is>
-          <t>Lanza espumígena de rodante</t>
+          <t>Sin cota en Fadesa</t>
         </is>
       </c>
       <c r="E77" s="45" t="inlineStr">
         <is>
-          <t>AFFF 50 l</t>
+          <t>7 modelos</t>
         </is>
       </c>
     </row>
@@ -24828,22 +25017,22 @@
       </c>
       <c r="B78" s="44" t="inlineStr">
         <is>
-          <t>flama/catalogo.py línea 135</t>
+          <t>flama/modelo3d.py línea 717</t>
         </is>
       </c>
       <c r="C78" s="45" t="inlineStr">
         <is>
-          <t>Cilindro sin costura: Espesor</t>
+          <t>Válvula esférica: Cuerpo × palanca</t>
         </is>
       </c>
       <c r="D78" s="45" t="inlineStr">
         <is>
-          <t>Pared para presión de ensayo 25 MPa (supuesto)</t>
+          <t>Representativa (comercial)</t>
         </is>
       </c>
       <c r="E78" s="45" t="inlineStr">
         <is>
-          <t>CO2 2 kg, CO2 5 kg</t>
+          <t>5 modelos</t>
         </is>
       </c>
     </row>
@@ -24855,22 +25044,22 @@
       </c>
       <c r="B79" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 354</t>
+          <t>flama/modelo3d.py línea 722</t>
         </is>
       </c>
       <c r="C79" s="45" t="inlineStr">
         <is>
-          <t>Disco de seguridad: Tapón hexagonal (entre caras × alto)</t>
+          <t>Lanza espumígena: Ø × largo</t>
         </is>
       </c>
       <c r="D79" s="45" t="inlineStr">
         <is>
-          <t>CO₂: disco de seguridad, rotura 18-21 MPa</t>
+          <t>Lanza espumígena de rodante</t>
         </is>
       </c>
       <c r="E79" s="45" t="inlineStr">
         <is>
-          <t>CO2 2 kg, CO2 5 kg</t>
+          <t>AFFF 50 l</t>
         </is>
       </c>
     </row>
@@ -24882,17 +25071,17 @@
       </c>
       <c r="B80" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 459</t>
+          <t>flama/catalogo.py línea 135</t>
         </is>
       </c>
       <c r="C80" s="45" t="inlineStr">
         <is>
-          <t>Pie de apoyo: Ø × alto</t>
+          <t>Cilindro sin costura: Espesor</t>
         </is>
       </c>
       <c r="D80" s="45" t="inlineStr">
         <is>
-          <t>Ø del cilindro × 0,55·R</t>
+          <t>Pared para presión de ensayo 25 MPa (supuesto)</t>
         </is>
       </c>
       <c r="E80" s="45" t="inlineStr">
@@ -24909,22 +25098,22 @@
       </c>
       <c r="B81" s="44" t="inlineStr">
         <is>
-          <t>flama/bom.py línea 225</t>
+          <t>flama/modelo3d.py línea 366</t>
         </is>
       </c>
       <c r="C81" s="45" t="inlineStr">
         <is>
-          <t>Cúpula: Ø del disco (referencia; el casquete se compra embutido); Fondo: Ø del disco (referencia; el casquete se compra embutido)</t>
+          <t>Disco de seguridad: Tapón hexagonal (entre caras × alto)</t>
         </is>
       </c>
       <c r="D81" s="45" t="inlineStr">
         <is>
-          <t>Ø = 2·√(superficie media / π) × 1,03 (recorte de pestaña); la define Gockel</t>
+          <t>CO₂: disco de seguridad, rotura 18-21 MPa</t>
         </is>
       </c>
       <c r="E81" s="45" t="inlineStr">
         <is>
-          <t>4 modelos</t>
+          <t>CO2 2 kg, CO2 5 kg</t>
         </is>
       </c>
     </row>
@@ -24936,20 +25125,74 @@
       </c>
       <c r="B82" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 705</t>
+          <t>flama/modelo3d.py línea 487</t>
         </is>
       </c>
       <c r="C82" s="45" t="inlineStr">
         <is>
+          <t>Pie de apoyo: Ø × alto</t>
+        </is>
+      </c>
+      <c r="D82" s="45" t="inlineStr">
+        <is>
+          <t>Ø del cilindro × 0,55·R</t>
+        </is>
+      </c>
+      <c r="E82" s="45" t="inlineStr">
+        <is>
+          <t>CO2 2 kg, CO2 5 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="43" t="inlineStr">
+        <is>
+          <t>D38</t>
+        </is>
+      </c>
+      <c r="B83" s="44" t="inlineStr">
+        <is>
+          <t>flama/bom.py línea 226</t>
+        </is>
+      </c>
+      <c r="C83" s="45" t="inlineStr">
+        <is>
+          <t>Cúpula: Ø del disco (referencia; el casquete se compra embutido); Fondo: Ø del disco (referencia; el casquete se compra embutido)</t>
+        </is>
+      </c>
+      <c r="D83" s="45" t="inlineStr">
+        <is>
+          <t>Ø = 2·√(superficie media / π) × 1,03 (recorte de pestaña); la define Gockel</t>
+        </is>
+      </c>
+      <c r="E83" s="45" t="inlineStr">
+        <is>
+          <t>4 modelos</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="43" t="inlineStr">
+        <is>
+          <t>D39</t>
+        </is>
+      </c>
+      <c r="B84" s="44" t="inlineStr">
+        <is>
+          <t>flama/modelo3d.py línea 733</t>
+        </is>
+      </c>
+      <c r="C84" s="45" t="inlineStr">
+        <is>
           <t>Tobera campana: Ø entrada / Ø boca × largo</t>
         </is>
       </c>
-      <c r="D82" s="45" t="inlineStr">
+      <c r="D84" s="45" t="inlineStr">
         <is>
           <t>Cono 16→34 de radio, 200 de largo</t>
         </is>
       </c>
-      <c r="E82" s="45" t="inlineStr">
+      <c r="E84" s="45" t="inlineStr">
         <is>
           <t>4 modelos</t>
         </is>
@@ -24994,6 +25237,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/salida/justificacion/Justificacion de medidas planos.xlsx
+++ b/salida/justificacion/Justificacion de medidas planos.xlsx
@@ -24106,7 +24106,7 @@
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>1: Numerado: desarrollo de 2,5-10 kg; en el 1 kg el número va en la cúpula; 2: Muesca de altura en el cuello (prensa Pannier); 3: Encastre: extremo del cuerpo reducido y fondo encastrado a presión; 4: Bordoneado: bordoneadora SWM-400; profundidad y posición del bordón  — Nota: Documento del usuario (no es la fuente de verdad: se usa para el paso a paso y las medidas que fija).</t>
+          <t>1: Numerado en el cuerpo (desarrollo de 2,5-10 kg). El documento pone el del 1 kg en la cúpula; criterio FLAMA: va en el cuerpo en todos los modelos; 2: Muesca de altura en el cuello (prensa Pannier); 3: Encastre: extremo del cuerpo reducido y fondo encastrado a presión; 4: Bordoneado: bordoneadora SWM-400; profundidad y posición del bordón  — Nota: Documento del usuario (no es la fuente de verdad: se usa para el paso a paso y las medidas que fija).</t>
         </is>
       </c>
       <c r="E43" s="19" t="inlineStr"/>
@@ -24114,7 +24114,7 @@
     <row r="44">
       <c r="A44" s="42" t="inlineStr">
         <is>
-          <t>Valores de diseño FLAMA (amarillo/naranja en las matrices). Links al commit 9cf9127.</t>
+          <t>Valores de diseño FLAMA (amarillo/naranja en las matrices). Links al commit 8b2bfec.</t>
         </is>
       </c>
     </row>
@@ -24342,7 +24342,7 @@
       </c>
       <c r="B53" s="44" t="inlineStr">
         <is>
-          <t>flama/modelo3d.py línea 851</t>
+          <t>flama/modelo3d.py línea 852</t>
         </is>
       </c>
       <c r="C53" s="45" t="inlineStr">
